--- a/selenium-tests/reports/Selenium_Website_Tests_300.xlsx
+++ b/selenium-tests/reports/Selenium_Website_Tests_300.xlsx
@@ -667,7 +667,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>7/25/2026, 2:25:16 PM</v>
+        <v>7/25/2026, 2:31:15 PM</v>
       </c>
     </row>
     <row r="13">
@@ -762,7 +762,7 @@
         <v>Chrome</v>
       </c>
       <c r="F2" s="5" t="str">
-        <v>1.44s</v>
+        <v>1.57s</v>
       </c>
       <c r="G2" s="5" t="str">
         <v>Successful login and redirect to dashboard/index page.</v>
@@ -797,7 +797,7 @@
         <v>Chrome</v>
       </c>
       <c r="F3" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.70s</v>
       </c>
       <c r="G3" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -832,7 +832,7 @@
         <v>Chrome</v>
       </c>
       <c r="F4" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.95s</v>
       </c>
       <c r="G4" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -867,7 +867,7 @@
         <v>Chrome</v>
       </c>
       <c r="F5" s="5" t="str">
-        <v>0.64s</v>
+        <v>0.68s</v>
       </c>
       <c r="G5" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -902,7 +902,7 @@
         <v>Chrome</v>
       </c>
       <c r="F6" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.70s</v>
       </c>
       <c r="G6" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -937,7 +937,7 @@
         <v>Chrome</v>
       </c>
       <c r="F7" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.71s</v>
       </c>
       <c r="G7" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -972,7 +972,7 @@
         <v>Chrome</v>
       </c>
       <c r="F8" s="5" t="str">
-        <v>0.65s</v>
+        <v>0.68s</v>
       </c>
       <c r="G8" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1042,7 +1042,7 @@
         <v>Chrome</v>
       </c>
       <c r="F10" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.66s</v>
       </c>
       <c r="G10" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1077,7 +1077,7 @@
         <v>Chrome</v>
       </c>
       <c r="F11" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.67s</v>
       </c>
       <c r="G11" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1112,7 +1112,7 @@
         <v>Chrome</v>
       </c>
       <c r="F12" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.68s</v>
       </c>
       <c r="G12" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1147,7 +1147,7 @@
         <v>Chrome</v>
       </c>
       <c r="F13" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.67s</v>
       </c>
       <c r="G13" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1182,7 +1182,7 @@
         <v>Chrome</v>
       </c>
       <c r="F14" s="5" t="str">
-        <v>0.65s</v>
+        <v>0.67s</v>
       </c>
       <c r="G14" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1217,7 +1217,7 @@
         <v>Chrome</v>
       </c>
       <c r="F15" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.71s</v>
       </c>
       <c r="G15" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1252,7 +1252,7 @@
         <v>Chrome</v>
       </c>
       <c r="F16" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.74s</v>
       </c>
       <c r="G16" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1287,7 +1287,7 @@
         <v>Chrome</v>
       </c>
       <c r="F17" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.71s</v>
       </c>
       <c r="G17" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1322,7 +1322,7 @@
         <v>Chrome</v>
       </c>
       <c r="F18" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.68s</v>
       </c>
       <c r="G18" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1357,7 +1357,7 @@
         <v>Chrome</v>
       </c>
       <c r="F19" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.67s</v>
       </c>
       <c r="G19" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1392,7 +1392,7 @@
         <v>Chrome</v>
       </c>
       <c r="F20" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.66s</v>
       </c>
       <c r="G20" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1427,7 +1427,7 @@
         <v>Chrome</v>
       </c>
       <c r="F21" s="5" t="str">
-        <v>0.65s</v>
+        <v>0.70s</v>
       </c>
       <c r="G21" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1462,7 +1462,7 @@
         <v>Chrome</v>
       </c>
       <c r="F22" s="5" t="str">
-        <v>0.70s</v>
+        <v>0.68s</v>
       </c>
       <c r="G22" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1497,7 +1497,7 @@
         <v>Chrome</v>
       </c>
       <c r="F23" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.65s</v>
       </c>
       <c r="G23" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1532,7 +1532,7 @@
         <v>Chrome</v>
       </c>
       <c r="F24" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.67s</v>
       </c>
       <c r="G24" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1567,7 +1567,7 @@
         <v>Chrome</v>
       </c>
       <c r="F25" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.64s</v>
       </c>
       <c r="G25" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1602,7 +1602,7 @@
         <v>Chrome</v>
       </c>
       <c r="F26" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.66s</v>
       </c>
       <c r="G26" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1637,7 +1637,7 @@
         <v>Chrome</v>
       </c>
       <c r="F27" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.70s</v>
       </c>
       <c r="G27" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1672,7 +1672,7 @@
         <v>Chrome</v>
       </c>
       <c r="F28" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.69s</v>
       </c>
       <c r="G28" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1707,7 +1707,7 @@
         <v>Chrome</v>
       </c>
       <c r="F29" s="5" t="str">
-        <v>0.64s</v>
+        <v>0.63s</v>
       </c>
       <c r="G29" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1742,7 +1742,7 @@
         <v>Chrome</v>
       </c>
       <c r="F30" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.69s</v>
       </c>
       <c r="G30" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1777,7 +1777,7 @@
         <v>Chrome</v>
       </c>
       <c r="F31" s="5" t="str">
-        <v>0.65s</v>
+        <v>0.66s</v>
       </c>
       <c r="G31" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1812,7 +1812,7 @@
         <v>Chrome</v>
       </c>
       <c r="F32" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.69s</v>
       </c>
       <c r="G32" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1847,7 +1847,7 @@
         <v>Chrome</v>
       </c>
       <c r="F33" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.67s</v>
       </c>
       <c r="G33" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1882,7 +1882,7 @@
         <v>Chrome</v>
       </c>
       <c r="F34" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.69s</v>
       </c>
       <c r="G34" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1917,7 +1917,7 @@
         <v>Chrome</v>
       </c>
       <c r="F35" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.67s</v>
       </c>
       <c r="G35" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1952,7 +1952,7 @@
         <v>Chrome</v>
       </c>
       <c r="F36" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.65s</v>
       </c>
       <c r="G36" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -1987,7 +1987,7 @@
         <v>Chrome</v>
       </c>
       <c r="F37" s="5" t="str">
-        <v>0.90s</v>
+        <v>0.84s</v>
       </c>
       <c r="G37" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2022,7 +2022,7 @@
         <v>Chrome</v>
       </c>
       <c r="F38" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.70s</v>
       </c>
       <c r="G38" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2057,7 +2057,7 @@
         <v>Chrome</v>
       </c>
       <c r="F39" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.65s</v>
       </c>
       <c r="G39" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2092,7 +2092,7 @@
         <v>Chrome</v>
       </c>
       <c r="F40" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.68s</v>
       </c>
       <c r="G40" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2127,7 +2127,7 @@
         <v>Chrome</v>
       </c>
       <c r="F41" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.70s</v>
       </c>
       <c r="G41" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2162,7 +2162,7 @@
         <v>Chrome</v>
       </c>
       <c r="F42" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.73s</v>
       </c>
       <c r="G42" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2197,7 +2197,7 @@
         <v>Chrome</v>
       </c>
       <c r="F43" s="5" t="str">
-        <v>0.64s</v>
+        <v>0.70s</v>
       </c>
       <c r="G43" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2232,7 +2232,7 @@
         <v>Chrome</v>
       </c>
       <c r="F44" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.67s</v>
       </c>
       <c r="G44" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2267,7 +2267,7 @@
         <v>Chrome</v>
       </c>
       <c r="F45" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.68s</v>
       </c>
       <c r="G45" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2302,7 +2302,7 @@
         <v>Chrome</v>
       </c>
       <c r="F46" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.68s</v>
       </c>
       <c r="G46" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2337,7 +2337,7 @@
         <v>Chrome</v>
       </c>
       <c r="F47" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.67s</v>
       </c>
       <c r="G47" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2372,7 +2372,7 @@
         <v>Chrome</v>
       </c>
       <c r="F48" s="5" t="str">
-        <v>0.69s</v>
+        <v>0.68s</v>
       </c>
       <c r="G48" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2407,7 +2407,7 @@
         <v>Chrome</v>
       </c>
       <c r="F49" s="5" t="str">
-        <v>0.66s</v>
+        <v>0.67s</v>
       </c>
       <c r="G49" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2442,7 +2442,7 @@
         <v>Chrome</v>
       </c>
       <c r="F50" s="5" t="str">
-        <v>0.68s</v>
+        <v>0.67s</v>
       </c>
       <c r="G50" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -2477,7 +2477,7 @@
         <v>Chrome</v>
       </c>
       <c r="F51" s="5" t="str">
-        <v>0.67s</v>
+        <v>0.68s</v>
       </c>
       <c r="G51" s="5" t="str">
         <v>Prevent submission or trigger email format validation warning.</v>
@@ -11318,13 +11318,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F2" s="5" t="str">
-        <v>17.2ms</v>
+        <v>47.2ms</v>
       </c>
       <c r="G2" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H2" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 17.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 47.2ms. Payload matches schema.</v>
       </c>
       <c r="I2" s="5" t="str">
         <v>PASS</v>
@@ -11350,13 +11350,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F3" s="5" t="str">
-        <v>21.4ms</v>
+        <v>34.6ms</v>
       </c>
       <c r="G3" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H3" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 21.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 34.6ms. Payload matches schema.</v>
       </c>
       <c r="I3" s="5" t="str">
         <v>PASS</v>
@@ -11382,13 +11382,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F4" s="5" t="str">
-        <v>59.3ms</v>
+        <v>33.4ms</v>
       </c>
       <c r="G4" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H4" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 59.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 33.4ms. Payload matches schema.</v>
       </c>
       <c r="I4" s="5" t="str">
         <v>PASS</v>
@@ -11414,13 +11414,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F5" s="5" t="str">
-        <v>59.8ms</v>
+        <v>24.6ms</v>
       </c>
       <c r="G5" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H5" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 59.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 24.6ms. Payload matches schema.</v>
       </c>
       <c r="I5" s="5" t="str">
         <v>PASS</v>
@@ -11446,13 +11446,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F6" s="5" t="str">
-        <v>24.0ms</v>
+        <v>14.8ms</v>
       </c>
       <c r="G6" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H6" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 24.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 14.8ms. Payload matches schema.</v>
       </c>
       <c r="I6" s="5" t="str">
         <v>PASS</v>
@@ -11478,13 +11478,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F7" s="5" t="str">
-        <v>53.2ms</v>
+        <v>41.0ms</v>
       </c>
       <c r="G7" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H7" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 53.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 41.0ms. Payload matches schema.</v>
       </c>
       <c r="I7" s="5" t="str">
         <v>PASS</v>
@@ -11510,13 +11510,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F8" s="5" t="str">
-        <v>19.5ms</v>
+        <v>45.6ms</v>
       </c>
       <c r="G8" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H8" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 19.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 45.6ms. Payload matches schema.</v>
       </c>
       <c r="I8" s="5" t="str">
         <v>PASS</v>
@@ -11542,13 +11542,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F9" s="5" t="str">
-        <v>24.0ms</v>
+        <v>44.0ms</v>
       </c>
       <c r="G9" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H9" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 24.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 44.0ms. Payload matches schema.</v>
       </c>
       <c r="I9" s="5" t="str">
         <v>PASS</v>
@@ -11606,13 +11606,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F11" s="5" t="str">
-        <v>43.8ms</v>
+        <v>24.1ms</v>
       </c>
       <c r="G11" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H11" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 43.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 24.1ms. Payload matches schema.</v>
       </c>
       <c r="I11" s="5" t="str">
         <v>PASS</v>
@@ -11638,13 +11638,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F12" s="5" t="str">
-        <v>26.7ms</v>
+        <v>23.9ms</v>
       </c>
       <c r="G12" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H12" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 26.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 23.9ms. Payload matches schema.</v>
       </c>
       <c r="I12" s="5" t="str">
         <v>PASS</v>
@@ -11670,13 +11670,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F13" s="5" t="str">
-        <v>56.1ms</v>
+        <v>14.6ms</v>
       </c>
       <c r="G13" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H13" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 56.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 14.6ms. Payload matches schema.</v>
       </c>
       <c r="I13" s="5" t="str">
         <v>PASS</v>
@@ -11702,13 +11702,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F14" s="5" t="str">
-        <v>46.2ms</v>
+        <v>49.8ms</v>
       </c>
       <c r="G14" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H14" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 46.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 49.8ms. Payload matches schema.</v>
       </c>
       <c r="I14" s="5" t="str">
         <v>PASS</v>
@@ -11734,13 +11734,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F15" s="5" t="str">
-        <v>17.1ms</v>
+        <v>51.7ms</v>
       </c>
       <c r="G15" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H15" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 17.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 51.7ms. Payload matches schema.</v>
       </c>
       <c r="I15" s="5" t="str">
         <v>PASS</v>
@@ -11766,13 +11766,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F16" s="5" t="str">
-        <v>41.7ms</v>
+        <v>48.4ms</v>
       </c>
       <c r="G16" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H16" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 41.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 48.4ms. Payload matches schema.</v>
       </c>
       <c r="I16" s="5" t="str">
         <v>PASS</v>
@@ -11798,13 +11798,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F17" s="5" t="str">
-        <v>27.1ms</v>
+        <v>33.7ms</v>
       </c>
       <c r="G17" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H17" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 27.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 33.7ms. Payload matches schema.</v>
       </c>
       <c r="I17" s="5" t="str">
         <v>PASS</v>
@@ -11830,13 +11830,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F18" s="5" t="str">
-        <v>42.0ms</v>
+        <v>16.4ms</v>
       </c>
       <c r="G18" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H18" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 42.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 16.4ms. Payload matches schema.</v>
       </c>
       <c r="I18" s="5" t="str">
         <v>PASS</v>
@@ -11862,13 +11862,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F19" s="5" t="str">
-        <v>28.3ms</v>
+        <v>24.6ms</v>
       </c>
       <c r="G19" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H19" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 28.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 24.6ms. Payload matches schema.</v>
       </c>
       <c r="I19" s="5" t="str">
         <v>PASS</v>
@@ -11894,13 +11894,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F20" s="5" t="str">
-        <v>31.0ms</v>
+        <v>18.1ms</v>
       </c>
       <c r="G20" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H20" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 31.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 18.1ms. Payload matches schema.</v>
       </c>
       <c r="I20" s="5" t="str">
         <v>PASS</v>
@@ -11926,13 +11926,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F21" s="5" t="str">
-        <v>25.1ms</v>
+        <v>51.6ms</v>
       </c>
       <c r="G21" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H21" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 25.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 51.6ms. Payload matches schema.</v>
       </c>
       <c r="I21" s="5" t="str">
         <v>PASS</v>
@@ -11958,13 +11958,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F22" s="5" t="str">
-        <v>41.9ms</v>
+        <v>12.1ms</v>
       </c>
       <c r="G22" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H22" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 41.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 12.1ms. Payload matches schema.</v>
       </c>
       <c r="I22" s="5" t="str">
         <v>PASS</v>
@@ -11990,13 +11990,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F23" s="5" t="str">
-        <v>12.5ms</v>
+        <v>34.9ms</v>
       </c>
       <c r="G23" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H23" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 12.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 34.9ms. Payload matches schema.</v>
       </c>
       <c r="I23" s="5" t="str">
         <v>PASS</v>
@@ -12022,13 +12022,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F24" s="5" t="str">
-        <v>56.4ms</v>
+        <v>39.4ms</v>
       </c>
       <c r="G24" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H24" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 56.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 39.4ms. Payload matches schema.</v>
       </c>
       <c r="I24" s="5" t="str">
         <v>PASS</v>
@@ -12054,13 +12054,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F25" s="5" t="str">
-        <v>20.7ms</v>
+        <v>53.3ms</v>
       </c>
       <c r="G25" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H25" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 20.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 53.3ms. Payload matches schema.</v>
       </c>
       <c r="I25" s="5" t="str">
         <v>PASS</v>
@@ -12086,13 +12086,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F26" s="5" t="str">
-        <v>41.7ms</v>
+        <v>25.6ms</v>
       </c>
       <c r="G26" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H26" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 41.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 25.6ms. Payload matches schema.</v>
       </c>
       <c r="I26" s="5" t="str">
         <v>PASS</v>
@@ -12118,13 +12118,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F27" s="5" t="str">
-        <v>12.2ms</v>
+        <v>13.8ms</v>
       </c>
       <c r="G27" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H27" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 12.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 13.8ms. Payload matches schema.</v>
       </c>
       <c r="I27" s="5" t="str">
         <v>PASS</v>
@@ -12150,13 +12150,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F28" s="5" t="str">
-        <v>45.4ms</v>
+        <v>32.1ms</v>
       </c>
       <c r="G28" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H28" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 45.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 32.1ms. Payload matches schema.</v>
       </c>
       <c r="I28" s="5" t="str">
         <v>PASS</v>
@@ -12182,13 +12182,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F29" s="5" t="str">
-        <v>48.5ms</v>
+        <v>26.2ms</v>
       </c>
       <c r="G29" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H29" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 48.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 26.2ms. Payload matches schema.</v>
       </c>
       <c r="I29" s="5" t="str">
         <v>PASS</v>
@@ -12214,13 +12214,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F30" s="5" t="str">
-        <v>54.4ms</v>
+        <v>43.0ms</v>
       </c>
       <c r="G30" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H30" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 54.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 43.0ms. Payload matches schema.</v>
       </c>
       <c r="I30" s="5" t="str">
         <v>PASS</v>
@@ -12246,13 +12246,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F31" s="5" t="str">
-        <v>20.4ms</v>
+        <v>25.4ms</v>
       </c>
       <c r="G31" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H31" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 20.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 25.4ms. Payload matches schema.</v>
       </c>
       <c r="I31" s="5" t="str">
         <v>PASS</v>
@@ -12278,13 +12278,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F32" s="5" t="str">
-        <v>15.5ms</v>
+        <v>38.2ms</v>
       </c>
       <c r="G32" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H32" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 15.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 38.2ms. Payload matches schema.</v>
       </c>
       <c r="I32" s="5" t="str">
         <v>PASS</v>
@@ -12310,13 +12310,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F33" s="5" t="str">
-        <v>15.8ms</v>
+        <v>30.6ms</v>
       </c>
       <c r="G33" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H33" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 15.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 30.6ms. Payload matches schema.</v>
       </c>
       <c r="I33" s="5" t="str">
         <v>PASS</v>
@@ -12342,13 +12342,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F34" s="5" t="str">
-        <v>43.3ms</v>
+        <v>21.5ms</v>
       </c>
       <c r="G34" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H34" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 43.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 21.5ms. Payload matches schema.</v>
       </c>
       <c r="I34" s="5" t="str">
         <v>PASS</v>
@@ -12374,13 +12374,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F35" s="5" t="str">
-        <v>38.1ms</v>
+        <v>33.9ms</v>
       </c>
       <c r="G35" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H35" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 38.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 33.9ms. Payload matches schema.</v>
       </c>
       <c r="I35" s="5" t="str">
         <v>PASS</v>
@@ -12406,13 +12406,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F36" s="5" t="str">
-        <v>47.9ms</v>
+        <v>23.9ms</v>
       </c>
       <c r="G36" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H36" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 47.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 23.9ms. Payload matches schema.</v>
       </c>
       <c r="I36" s="5" t="str">
         <v>PASS</v>
@@ -12438,13 +12438,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F37" s="5" t="str">
-        <v>27.6ms</v>
+        <v>59.6ms</v>
       </c>
       <c r="G37" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H37" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 27.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 59.6ms. Payload matches schema.</v>
       </c>
       <c r="I37" s="5" t="str">
         <v>PASS</v>
@@ -12470,13 +12470,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F38" s="5" t="str">
-        <v>12.8ms</v>
+        <v>54.3ms</v>
       </c>
       <c r="G38" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H38" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 12.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 54.3ms. Payload matches schema.</v>
       </c>
       <c r="I38" s="5" t="str">
         <v>PASS</v>
@@ -12502,13 +12502,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F39" s="5" t="str">
-        <v>23.3ms</v>
+        <v>49.8ms</v>
       </c>
       <c r="G39" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H39" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 23.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 49.8ms. Payload matches schema.</v>
       </c>
       <c r="I39" s="5" t="str">
         <v>PASS</v>
@@ -12534,13 +12534,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F40" s="5" t="str">
-        <v>46.3ms</v>
+        <v>13.3ms</v>
       </c>
       <c r="G40" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H40" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 46.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 13.3ms. Payload matches schema.</v>
       </c>
       <c r="I40" s="5" t="str">
         <v>PASS</v>
@@ -12566,13 +12566,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F41" s="5" t="str">
-        <v>54.9ms</v>
+        <v>31.8ms</v>
       </c>
       <c r="G41" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H41" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 54.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 31.8ms. Payload matches schema.</v>
       </c>
       <c r="I41" s="5" t="str">
         <v>PASS</v>
@@ -12598,13 +12598,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F42" s="5" t="str">
-        <v>15.5ms</v>
+        <v>39.8ms</v>
       </c>
       <c r="G42" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H42" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 15.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 39.8ms. Payload matches schema.</v>
       </c>
       <c r="I42" s="5" t="str">
         <v>PASS</v>
@@ -12630,13 +12630,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F43" s="5" t="str">
-        <v>58.9ms</v>
+        <v>23.6ms</v>
       </c>
       <c r="G43" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H43" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 58.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 23.6ms. Payload matches schema.</v>
       </c>
       <c r="I43" s="5" t="str">
         <v>PASS</v>
@@ -12662,13 +12662,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F44" s="5" t="str">
-        <v>47.5ms</v>
+        <v>35.5ms</v>
       </c>
       <c r="G44" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H44" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 47.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 35.5ms. Payload matches schema.</v>
       </c>
       <c r="I44" s="5" t="str">
         <v>PASS</v>
@@ -12694,13 +12694,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F45" s="5" t="str">
-        <v>39.2ms</v>
+        <v>29.9ms</v>
       </c>
       <c r="G45" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H45" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 39.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 29.9ms. Payload matches schema.</v>
       </c>
       <c r="I45" s="5" t="str">
         <v>PASS</v>
@@ -12726,13 +12726,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F46" s="5" t="str">
-        <v>33.1ms</v>
+        <v>53.6ms</v>
       </c>
       <c r="G46" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H46" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 33.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 53.6ms. Payload matches schema.</v>
       </c>
       <c r="I46" s="5" t="str">
         <v>PASS</v>
@@ -12758,13 +12758,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F47" s="5" t="str">
-        <v>45.6ms</v>
+        <v>55.4ms</v>
       </c>
       <c r="G47" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H47" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 45.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 55.4ms. Payload matches schema.</v>
       </c>
       <c r="I47" s="5" t="str">
         <v>PASS</v>
@@ -12790,13 +12790,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F48" s="5" t="str">
-        <v>51.3ms</v>
+        <v>59.1ms</v>
       </c>
       <c r="G48" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H48" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 51.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 59.1ms. Payload matches schema.</v>
       </c>
       <c r="I48" s="5" t="str">
         <v>PASS</v>
@@ -12822,13 +12822,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F49" s="5" t="str">
-        <v>11.4ms</v>
+        <v>12.9ms</v>
       </c>
       <c r="G49" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H49" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 11.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 12.9ms. Payload matches schema.</v>
       </c>
       <c r="I49" s="5" t="str">
         <v>PASS</v>
@@ -12854,13 +12854,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F50" s="5" t="str">
-        <v>16.0ms</v>
+        <v>48.2ms</v>
       </c>
       <c r="G50" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H50" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 16.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 48.2ms. Payload matches schema.</v>
       </c>
       <c r="I50" s="5" t="str">
         <v>PASS</v>
@@ -12886,13 +12886,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F51" s="5" t="str">
-        <v>49.8ms</v>
+        <v>44.2ms</v>
       </c>
       <c r="G51" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H51" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 49.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 44.2ms. Payload matches schema.</v>
       </c>
       <c r="I51" s="5" t="str">
         <v>PASS</v>
@@ -12918,13 +12918,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F52" s="5" t="str">
-        <v>44.9ms</v>
+        <v>11.6ms</v>
       </c>
       <c r="G52" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H52" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 44.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 11.6ms. Payload matches schema.</v>
       </c>
       <c r="I52" s="5" t="str">
         <v>PASS</v>
@@ -12950,13 +12950,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F53" s="5" t="str">
-        <v>43.3ms</v>
+        <v>29.0ms</v>
       </c>
       <c r="G53" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H53" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 43.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 29.0ms. Payload matches schema.</v>
       </c>
       <c r="I53" s="5" t="str">
         <v>PASS</v>
@@ -12982,13 +12982,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F54" s="5" t="str">
-        <v>28.9ms</v>
+        <v>50.7ms</v>
       </c>
       <c r="G54" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H54" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 28.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 50.7ms. Payload matches schema.</v>
       </c>
       <c r="I54" s="5" t="str">
         <v>PASS</v>
@@ -13014,13 +13014,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F55" s="5" t="str">
-        <v>41.0ms</v>
+        <v>35.7ms</v>
       </c>
       <c r="G55" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H55" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 41.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 35.7ms. Payload matches schema.</v>
       </c>
       <c r="I55" s="5" t="str">
         <v>PASS</v>
@@ -13046,13 +13046,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F56" s="5" t="str">
-        <v>35.0ms</v>
+        <v>15.8ms</v>
       </c>
       <c r="G56" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H56" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 35.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 15.8ms. Payload matches schema.</v>
       </c>
       <c r="I56" s="5" t="str">
         <v>PASS</v>
@@ -13078,13 +13078,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F57" s="5" t="str">
-        <v>45.4ms</v>
+        <v>26.1ms</v>
       </c>
       <c r="G57" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H57" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 45.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 26.1ms. Payload matches schema.</v>
       </c>
       <c r="I57" s="5" t="str">
         <v>PASS</v>
@@ -13110,13 +13110,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F58" s="5" t="str">
-        <v>31.5ms</v>
+        <v>53.5ms</v>
       </c>
       <c r="G58" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H58" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 31.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 53.5ms. Payload matches schema.</v>
       </c>
       <c r="I58" s="5" t="str">
         <v>PASS</v>
@@ -13142,13 +13142,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F59" s="5" t="str">
-        <v>51.9ms</v>
+        <v>33.0ms</v>
       </c>
       <c r="G59" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H59" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 51.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 33.0ms. Payload matches schema.</v>
       </c>
       <c r="I59" s="5" t="str">
         <v>PASS</v>
@@ -13174,13 +13174,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F60" s="5" t="str">
-        <v>21.3ms</v>
+        <v>13.0ms</v>
       </c>
       <c r="G60" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H60" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 21.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 13.0ms. Payload matches schema.</v>
       </c>
       <c r="I60" s="5" t="str">
         <v>PASS</v>
@@ -13206,13 +13206,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F61" s="5" t="str">
-        <v>16.8ms</v>
+        <v>46.3ms</v>
       </c>
       <c r="G61" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H61" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 16.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 46.3ms. Payload matches schema.</v>
       </c>
       <c r="I61" s="5" t="str">
         <v>PASS</v>
@@ -13238,13 +13238,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F62" s="5" t="str">
-        <v>38.7ms</v>
+        <v>35.3ms</v>
       </c>
       <c r="G62" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H62" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 38.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 35.3ms. Payload matches schema.</v>
       </c>
       <c r="I62" s="5" t="str">
         <v>PASS</v>
@@ -13270,13 +13270,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F63" s="5" t="str">
-        <v>42.5ms</v>
+        <v>46.7ms</v>
       </c>
       <c r="G63" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H63" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 42.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 46.7ms. Payload matches schema.</v>
       </c>
       <c r="I63" s="5" t="str">
         <v>PASS</v>
@@ -13302,13 +13302,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F64" s="5" t="str">
-        <v>37.4ms</v>
+        <v>27.1ms</v>
       </c>
       <c r="G64" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H64" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 37.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 27.1ms. Payload matches schema.</v>
       </c>
       <c r="I64" s="5" t="str">
         <v>PASS</v>
@@ -13334,13 +13334,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F65" s="5" t="str">
-        <v>15.4ms</v>
+        <v>13.3ms</v>
       </c>
       <c r="G65" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H65" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 15.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 13.3ms. Payload matches schema.</v>
       </c>
       <c r="I65" s="5" t="str">
         <v>PASS</v>
@@ -13366,13 +13366,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F66" s="5" t="str">
-        <v>54.8ms</v>
+        <v>52.9ms</v>
       </c>
       <c r="G66" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H66" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 54.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 52.9ms. Payload matches schema.</v>
       </c>
       <c r="I66" s="5" t="str">
         <v>PASS</v>
@@ -13398,13 +13398,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F67" s="5" t="str">
-        <v>15.8ms</v>
+        <v>23.9ms</v>
       </c>
       <c r="G67" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H67" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 15.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 23.9ms. Payload matches schema.</v>
       </c>
       <c r="I67" s="5" t="str">
         <v>PASS</v>
@@ -13430,13 +13430,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F68" s="5" t="str">
-        <v>18.5ms</v>
+        <v>40.7ms</v>
       </c>
       <c r="G68" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H68" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 18.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 40.7ms. Payload matches schema.</v>
       </c>
       <c r="I68" s="5" t="str">
         <v>PASS</v>
@@ -13462,13 +13462,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F69" s="5" t="str">
-        <v>56.0ms</v>
+        <v>22.4ms</v>
       </c>
       <c r="G69" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H69" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 56.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 22.4ms. Payload matches schema.</v>
       </c>
       <c r="I69" s="5" t="str">
         <v>PASS</v>
@@ -13494,13 +13494,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F70" s="5" t="str">
-        <v>28.2ms</v>
+        <v>33.9ms</v>
       </c>
       <c r="G70" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H70" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 28.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 33.9ms. Payload matches schema.</v>
       </c>
       <c r="I70" s="5" t="str">
         <v>PASS</v>
@@ -13526,13 +13526,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F71" s="5" t="str">
-        <v>41.3ms</v>
+        <v>10.8ms</v>
       </c>
       <c r="G71" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H71" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 41.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 10.8ms. Payload matches schema.</v>
       </c>
       <c r="I71" s="5" t="str">
         <v>PASS</v>
@@ -13558,13 +13558,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F72" s="5" t="str">
-        <v>56.9ms</v>
+        <v>42.0ms</v>
       </c>
       <c r="G72" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H72" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 56.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 42.0ms. Payload matches schema.</v>
       </c>
       <c r="I72" s="5" t="str">
         <v>PASS</v>
@@ -13590,13 +13590,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F73" s="5" t="str">
-        <v>44.5ms</v>
+        <v>42.1ms</v>
       </c>
       <c r="G73" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H73" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 44.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 42.1ms. Payload matches schema.</v>
       </c>
       <c r="I73" s="5" t="str">
         <v>PASS</v>
@@ -13622,13 +13622,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F74" s="5" t="str">
-        <v>56.6ms</v>
+        <v>17.1ms</v>
       </c>
       <c r="G74" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H74" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 56.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 17.1ms. Payload matches schema.</v>
       </c>
       <c r="I74" s="5" t="str">
         <v>PASS</v>
@@ -13654,13 +13654,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F75" s="5" t="str">
-        <v>15.3ms</v>
+        <v>47.9ms</v>
       </c>
       <c r="G75" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H75" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 15.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 47.9ms. Payload matches schema.</v>
       </c>
       <c r="I75" s="5" t="str">
         <v>PASS</v>
@@ -13686,13 +13686,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F76" s="5" t="str">
-        <v>27.3ms</v>
+        <v>30.4ms</v>
       </c>
       <c r="G76" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H76" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 27.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 30.4ms. Payload matches schema.</v>
       </c>
       <c r="I76" s="5" t="str">
         <v>PASS</v>
@@ -13718,13 +13718,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F77" s="5" t="str">
-        <v>41.7ms</v>
+        <v>47.9ms</v>
       </c>
       <c r="G77" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H77" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 41.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 47.9ms. Payload matches schema.</v>
       </c>
       <c r="I77" s="5" t="str">
         <v>PASS</v>
@@ -13750,13 +13750,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F78" s="5" t="str">
-        <v>58.2ms</v>
+        <v>53.4ms</v>
       </c>
       <c r="G78" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H78" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 58.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 53.4ms. Payload matches schema.</v>
       </c>
       <c r="I78" s="5" t="str">
         <v>PASS</v>
@@ -13782,13 +13782,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F79" s="5" t="str">
-        <v>30.9ms</v>
+        <v>59.4ms</v>
       </c>
       <c r="G79" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H79" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 30.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 59.4ms. Payload matches schema.</v>
       </c>
       <c r="I79" s="5" t="str">
         <v>PASS</v>
@@ -13814,13 +13814,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F80" s="5" t="str">
-        <v>18.8ms</v>
+        <v>30.0ms</v>
       </c>
       <c r="G80" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H80" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 18.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 30.0ms. Payload matches schema.</v>
       </c>
       <c r="I80" s="5" t="str">
         <v>PASS</v>
@@ -13846,13 +13846,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F81" s="5" t="str">
-        <v>17.3ms</v>
+        <v>47.6ms</v>
       </c>
       <c r="G81" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H81" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 17.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 47.6ms. Payload matches schema.</v>
       </c>
       <c r="I81" s="5" t="str">
         <v>PASS</v>
@@ -13878,13 +13878,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F82" s="5" t="str">
-        <v>20.3ms</v>
+        <v>17.1ms</v>
       </c>
       <c r="G82" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H82" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 20.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 17.1ms. Payload matches schema.</v>
       </c>
       <c r="I82" s="5" t="str">
         <v>PASS</v>
@@ -13910,13 +13910,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F83" s="5" t="str">
-        <v>12.3ms</v>
+        <v>32.2ms</v>
       </c>
       <c r="G83" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H83" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 12.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 32.2ms. Payload matches schema.</v>
       </c>
       <c r="I83" s="5" t="str">
         <v>PASS</v>
@@ -13942,13 +13942,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F84" s="5" t="str">
-        <v>28.4ms</v>
+        <v>40.3ms</v>
       </c>
       <c r="G84" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H84" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 28.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 40.3ms. Payload matches schema.</v>
       </c>
       <c r="I84" s="5" t="str">
         <v>PASS</v>
@@ -13974,13 +13974,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F85" s="5" t="str">
-        <v>47.3ms</v>
+        <v>27.5ms</v>
       </c>
       <c r="G85" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H85" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 47.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 27.5ms. Payload matches schema.</v>
       </c>
       <c r="I85" s="5" t="str">
         <v>PASS</v>
@@ -14006,13 +14006,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F86" s="5" t="str">
-        <v>30.2ms</v>
+        <v>16.9ms</v>
       </c>
       <c r="G86" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H86" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 30.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 16.9ms. Payload matches schema.</v>
       </c>
       <c r="I86" s="5" t="str">
         <v>PASS</v>
@@ -14038,13 +14038,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F87" s="5" t="str">
-        <v>47.3ms</v>
+        <v>59.3ms</v>
       </c>
       <c r="G87" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H87" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 47.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 59.3ms. Payload matches schema.</v>
       </c>
       <c r="I87" s="5" t="str">
         <v>PASS</v>
@@ -14070,13 +14070,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F88" s="5" t="str">
-        <v>49.6ms</v>
+        <v>25.7ms</v>
       </c>
       <c r="G88" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H88" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 49.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 25.7ms. Payload matches schema.</v>
       </c>
       <c r="I88" s="5" t="str">
         <v>PASS</v>
@@ -14102,13 +14102,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F89" s="5" t="str">
-        <v>18.5ms</v>
+        <v>51.4ms</v>
       </c>
       <c r="G89" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H89" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 18.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 51.4ms. Payload matches schema.</v>
       </c>
       <c r="I89" s="5" t="str">
         <v>PASS</v>
@@ -14134,13 +14134,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F90" s="5" t="str">
-        <v>17.5ms</v>
+        <v>52.1ms</v>
       </c>
       <c r="G90" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H90" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 17.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 52.1ms. Payload matches schema.</v>
       </c>
       <c r="I90" s="5" t="str">
         <v>PASS</v>
@@ -14166,13 +14166,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F91" s="5" t="str">
-        <v>51.0ms</v>
+        <v>49.3ms</v>
       </c>
       <c r="G91" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H91" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 51.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 49.3ms. Payload matches schema.</v>
       </c>
       <c r="I91" s="5" t="str">
         <v>PASS</v>
@@ -14198,13 +14198,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F92" s="5" t="str">
-        <v>22.8ms</v>
+        <v>24.0ms</v>
       </c>
       <c r="G92" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H92" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 22.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 24.0ms. Payload matches schema.</v>
       </c>
       <c r="I92" s="5" t="str">
         <v>PASS</v>
@@ -14230,13 +14230,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F93" s="5" t="str">
-        <v>49.8ms</v>
+        <v>10.8ms</v>
       </c>
       <c r="G93" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H93" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 49.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 10.8ms. Payload matches schema.</v>
       </c>
       <c r="I93" s="5" t="str">
         <v>PASS</v>
@@ -14262,13 +14262,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F94" s="5" t="str">
-        <v>46.1ms</v>
+        <v>53.5ms</v>
       </c>
       <c r="G94" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H94" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 46.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 53.5ms. Payload matches schema.</v>
       </c>
       <c r="I94" s="5" t="str">
         <v>PASS</v>
@@ -14294,13 +14294,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F95" s="5" t="str">
-        <v>20.5ms</v>
+        <v>51.2ms</v>
       </c>
       <c r="G95" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H95" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 20.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 51.2ms. Payload matches schema.</v>
       </c>
       <c r="I95" s="5" t="str">
         <v>PASS</v>
@@ -14326,13 +14326,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F96" s="5" t="str">
-        <v>31.0ms</v>
+        <v>57.9ms</v>
       </c>
       <c r="G96" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H96" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 31.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 57.9ms. Payload matches schema.</v>
       </c>
       <c r="I96" s="5" t="str">
         <v>PASS</v>
@@ -14358,13 +14358,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F97" s="5" t="str">
-        <v>29.8ms</v>
+        <v>12.9ms</v>
       </c>
       <c r="G97" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H97" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 29.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 12.9ms. Payload matches schema.</v>
       </c>
       <c r="I97" s="5" t="str">
         <v>PASS</v>
@@ -14390,13 +14390,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F98" s="5" t="str">
-        <v>51.7ms</v>
+        <v>13.1ms</v>
       </c>
       <c r="G98" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H98" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 51.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 13.1ms. Payload matches schema.</v>
       </c>
       <c r="I98" s="5" t="str">
         <v>PASS</v>
@@ -14422,13 +14422,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F99" s="5" t="str">
-        <v>40.1ms</v>
+        <v>40.7ms</v>
       </c>
       <c r="G99" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H99" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 40.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 40.7ms. Payload matches schema.</v>
       </c>
       <c r="I99" s="5" t="str">
         <v>PASS</v>
@@ -14454,13 +14454,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F100" s="5" t="str">
-        <v>31.8ms</v>
+        <v>21.1ms</v>
       </c>
       <c r="G100" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H100" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 31.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 21.1ms. Payload matches schema.</v>
       </c>
       <c r="I100" s="5" t="str">
         <v>PASS</v>
@@ -14486,13 +14486,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F101" s="5" t="str">
-        <v>12.9ms</v>
+        <v>47.9ms</v>
       </c>
       <c r="G101" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H101" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 12.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 47.9ms. Payload matches schema.</v>
       </c>
       <c r="I101" s="5" t="str">
         <v>PASS</v>
@@ -14518,13 +14518,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F102" s="5" t="str">
-        <v>40.5ms</v>
+        <v>29.3ms</v>
       </c>
       <c r="G102" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H102" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 40.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 29.3ms. Payload matches schema.</v>
       </c>
       <c r="I102" s="5" t="str">
         <v>PASS</v>
@@ -14550,13 +14550,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F103" s="5" t="str">
-        <v>47.8ms</v>
+        <v>17.1ms</v>
       </c>
       <c r="G103" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H103" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 47.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 17.1ms. Payload matches schema.</v>
       </c>
       <c r="I103" s="5" t="str">
         <v>PASS</v>
@@ -14582,13 +14582,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F104" s="5" t="str">
-        <v>59.4ms</v>
+        <v>51.7ms</v>
       </c>
       <c r="G104" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H104" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 59.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 51.7ms. Payload matches schema.</v>
       </c>
       <c r="I104" s="5" t="str">
         <v>PASS</v>
@@ -14614,13 +14614,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F105" s="5" t="str">
-        <v>34.5ms</v>
+        <v>25.5ms</v>
       </c>
       <c r="G105" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H105" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 34.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 25.5ms. Payload matches schema.</v>
       </c>
       <c r="I105" s="5" t="str">
         <v>PASS</v>
@@ -14646,13 +14646,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F106" s="5" t="str">
-        <v>44.6ms</v>
+        <v>10.8ms</v>
       </c>
       <c r="G106" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H106" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 44.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 10.8ms. Payload matches schema.</v>
       </c>
       <c r="I106" s="5" t="str">
         <v>PASS</v>
@@ -14678,13 +14678,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F107" s="5" t="str">
-        <v>48.1ms</v>
+        <v>21.6ms</v>
       </c>
       <c r="G107" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H107" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 48.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 21.6ms. Payload matches schema.</v>
       </c>
       <c r="I107" s="5" t="str">
         <v>PASS</v>
@@ -14710,13 +14710,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F108" s="5" t="str">
-        <v>51.4ms</v>
+        <v>56.5ms</v>
       </c>
       <c r="G108" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H108" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 51.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 56.5ms. Payload matches schema.</v>
       </c>
       <c r="I108" s="5" t="str">
         <v>PASS</v>
@@ -14742,13 +14742,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F109" s="5" t="str">
-        <v>37.0ms</v>
+        <v>25.3ms</v>
       </c>
       <c r="G109" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H109" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 37.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 25.3ms. Payload matches schema.</v>
       </c>
       <c r="I109" s="5" t="str">
         <v>PASS</v>
@@ -14774,13 +14774,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F110" s="5" t="str">
-        <v>21.6ms</v>
+        <v>10.7ms</v>
       </c>
       <c r="G110" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H110" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 21.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 10.7ms. Payload matches schema.</v>
       </c>
       <c r="I110" s="5" t="str">
         <v>PASS</v>
@@ -14806,13 +14806,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F111" s="5" t="str">
-        <v>21.5ms</v>
+        <v>48.4ms</v>
       </c>
       <c r="G111" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H111" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 21.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 48.4ms. Payload matches schema.</v>
       </c>
       <c r="I111" s="5" t="str">
         <v>PASS</v>
@@ -14838,13 +14838,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F112" s="5" t="str">
-        <v>32.8ms</v>
+        <v>15.9ms</v>
       </c>
       <c r="G112" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H112" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 32.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 15.9ms. Payload matches schema.</v>
       </c>
       <c r="I112" s="5" t="str">
         <v>PASS</v>
@@ -14870,13 +14870,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F113" s="5" t="str">
-        <v>58.4ms</v>
+        <v>54.7ms</v>
       </c>
       <c r="G113" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H113" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 58.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 54.7ms. Payload matches schema.</v>
       </c>
       <c r="I113" s="5" t="str">
         <v>PASS</v>
@@ -14902,13 +14902,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F114" s="5" t="str">
-        <v>47.5ms</v>
+        <v>16.7ms</v>
       </c>
       <c r="G114" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H114" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 47.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 16.7ms. Payload matches schema.</v>
       </c>
       <c r="I114" s="5" t="str">
         <v>PASS</v>
@@ -14934,13 +14934,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F115" s="5" t="str">
-        <v>18.2ms</v>
+        <v>18.1ms</v>
       </c>
       <c r="G115" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H115" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 18.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 18.1ms. Payload matches schema.</v>
       </c>
       <c r="I115" s="5" t="str">
         <v>PASS</v>
@@ -14966,13 +14966,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F116" s="5" t="str">
-        <v>56.9ms</v>
+        <v>45.0ms</v>
       </c>
       <c r="G116" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H116" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 56.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 45.0ms. Payload matches schema.</v>
       </c>
       <c r="I116" s="5" t="str">
         <v>PASS</v>
@@ -14998,13 +14998,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F117" s="5" t="str">
-        <v>43.2ms</v>
+        <v>21.1ms</v>
       </c>
       <c r="G117" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H117" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 43.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 21.1ms. Payload matches schema.</v>
       </c>
       <c r="I117" s="5" t="str">
         <v>PASS</v>
@@ -15030,13 +15030,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F118" s="5" t="str">
-        <v>52.7ms</v>
+        <v>28.2ms</v>
       </c>
       <c r="G118" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H118" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 52.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 28.2ms. Payload matches schema.</v>
       </c>
       <c r="I118" s="5" t="str">
         <v>PASS</v>
@@ -15094,13 +15094,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F120" s="5" t="str">
-        <v>15.5ms</v>
+        <v>16.7ms</v>
       </c>
       <c r="G120" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H120" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 15.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 16.7ms. Payload matches schema.</v>
       </c>
       <c r="I120" s="5" t="str">
         <v>PASS</v>
@@ -15126,13 +15126,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F121" s="5" t="str">
-        <v>56.8ms</v>
+        <v>53.6ms</v>
       </c>
       <c r="G121" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H121" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 56.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 53.6ms. Payload matches schema.</v>
       </c>
       <c r="I121" s="5" t="str">
         <v>PASS</v>
@@ -15158,13 +15158,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F122" s="5" t="str">
-        <v>11.3ms</v>
+        <v>55.6ms</v>
       </c>
       <c r="G122" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H122" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 11.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 55.6ms. Payload matches schema.</v>
       </c>
       <c r="I122" s="5" t="str">
         <v>PASS</v>
@@ -15190,13 +15190,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F123" s="5" t="str">
-        <v>22.1ms</v>
+        <v>44.6ms</v>
       </c>
       <c r="G123" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H123" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 22.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 44.6ms. Payload matches schema.</v>
       </c>
       <c r="I123" s="5" t="str">
         <v>PASS</v>
@@ -15222,13 +15222,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F124" s="5" t="str">
-        <v>11.9ms</v>
+        <v>37.7ms</v>
       </c>
       <c r="G124" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H124" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 11.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 37.7ms. Payload matches schema.</v>
       </c>
       <c r="I124" s="5" t="str">
         <v>PASS</v>
@@ -15254,13 +15254,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F125" s="5" t="str">
-        <v>15.1ms</v>
+        <v>50.7ms</v>
       </c>
       <c r="G125" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H125" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 15.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 50.7ms. Payload matches schema.</v>
       </c>
       <c r="I125" s="5" t="str">
         <v>PASS</v>
@@ -15286,13 +15286,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F126" s="5" t="str">
-        <v>38.2ms</v>
+        <v>40.7ms</v>
       </c>
       <c r="G126" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H126" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 38.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 40.7ms. Payload matches schema.</v>
       </c>
       <c r="I126" s="5" t="str">
         <v>PASS</v>
@@ -15318,13 +15318,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F127" s="5" t="str">
-        <v>38.6ms</v>
+        <v>13.0ms</v>
       </c>
       <c r="G127" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H127" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 38.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 13.0ms. Payload matches schema.</v>
       </c>
       <c r="I127" s="5" t="str">
         <v>PASS</v>
@@ -15350,13 +15350,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F128" s="5" t="str">
-        <v>41.1ms</v>
+        <v>17.5ms</v>
       </c>
       <c r="G128" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H128" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 41.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 17.5ms. Payload matches schema.</v>
       </c>
       <c r="I128" s="5" t="str">
         <v>PASS</v>
@@ -15382,13 +15382,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F129" s="5" t="str">
-        <v>33.8ms</v>
+        <v>21.5ms</v>
       </c>
       <c r="G129" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H129" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 33.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 21.5ms. Payload matches schema.</v>
       </c>
       <c r="I129" s="5" t="str">
         <v>PASS</v>
@@ -15414,13 +15414,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F130" s="5" t="str">
-        <v>34.2ms</v>
+        <v>21.0ms</v>
       </c>
       <c r="G130" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H130" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 34.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 21.0ms. Payload matches schema.</v>
       </c>
       <c r="I130" s="5" t="str">
         <v>PASS</v>
@@ -15446,13 +15446,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F131" s="5" t="str">
-        <v>56.6ms</v>
+        <v>16.3ms</v>
       </c>
       <c r="G131" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H131" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 56.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 16.3ms. Payload matches schema.</v>
       </c>
       <c r="I131" s="5" t="str">
         <v>PASS</v>
@@ -15478,13 +15478,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F132" s="5" t="str">
-        <v>37.2ms</v>
+        <v>43.4ms</v>
       </c>
       <c r="G132" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H132" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 37.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 43.4ms. Payload matches schema.</v>
       </c>
       <c r="I132" s="5" t="str">
         <v>PASS</v>
@@ -15510,13 +15510,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F133" s="5" t="str">
-        <v>36.4ms</v>
+        <v>11.7ms</v>
       </c>
       <c r="G133" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H133" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 36.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 11.7ms. Payload matches schema.</v>
       </c>
       <c r="I133" s="5" t="str">
         <v>PASS</v>
@@ -15542,13 +15542,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F134" s="5" t="str">
-        <v>38.0ms</v>
+        <v>11.2ms</v>
       </c>
       <c r="G134" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H134" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 38.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 11.2ms. Payload matches schema.</v>
       </c>
       <c r="I134" s="5" t="str">
         <v>PASS</v>
@@ -15574,13 +15574,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F135" s="5" t="str">
-        <v>57.1ms</v>
+        <v>17.7ms</v>
       </c>
       <c r="G135" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H135" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 57.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 17.7ms. Payload matches schema.</v>
       </c>
       <c r="I135" s="5" t="str">
         <v>PASS</v>
@@ -15606,13 +15606,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F136" s="5" t="str">
-        <v>10.7ms</v>
+        <v>42.6ms</v>
       </c>
       <c r="G136" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H136" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 10.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 42.6ms. Payload matches schema.</v>
       </c>
       <c r="I136" s="5" t="str">
         <v>PASS</v>
@@ -15638,13 +15638,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F137" s="5" t="str">
-        <v>45.7ms</v>
+        <v>44.5ms</v>
       </c>
       <c r="G137" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H137" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 45.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 44.5ms. Payload matches schema.</v>
       </c>
       <c r="I137" s="5" t="str">
         <v>PASS</v>
@@ -15670,13 +15670,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F138" s="5" t="str">
-        <v>48.5ms</v>
+        <v>28.5ms</v>
       </c>
       <c r="G138" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H138" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 48.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 28.5ms. Payload matches schema.</v>
       </c>
       <c r="I138" s="5" t="str">
         <v>PASS</v>
@@ -15702,13 +15702,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F139" s="5" t="str">
-        <v>20.7ms</v>
+        <v>30.4ms</v>
       </c>
       <c r="G139" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H139" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 20.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 30.4ms. Payload matches schema.</v>
       </c>
       <c r="I139" s="5" t="str">
         <v>PASS</v>
@@ -15734,13 +15734,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F140" s="5" t="str">
-        <v>31.1ms</v>
+        <v>28.0ms</v>
       </c>
       <c r="G140" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H140" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 31.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 28.0ms. Payload matches schema.</v>
       </c>
       <c r="I140" s="5" t="str">
         <v>PASS</v>
@@ -15766,13 +15766,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F141" s="5" t="str">
-        <v>18.7ms</v>
+        <v>29.5ms</v>
       </c>
       <c r="G141" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H141" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 18.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 29.5ms. Payload matches schema.</v>
       </c>
       <c r="I141" s="5" t="str">
         <v>PASS</v>
@@ -15798,13 +15798,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F142" s="5" t="str">
-        <v>34.1ms</v>
+        <v>56.2ms</v>
       </c>
       <c r="G142" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H142" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 34.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 56.2ms. Payload matches schema.</v>
       </c>
       <c r="I142" s="5" t="str">
         <v>PASS</v>
@@ -15830,13 +15830,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F143" s="5" t="str">
-        <v>31.6ms</v>
+        <v>47.0ms</v>
       </c>
       <c r="G143" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H143" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 31.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 47.0ms. Payload matches schema.</v>
       </c>
       <c r="I143" s="5" t="str">
         <v>PASS</v>
@@ -15862,13 +15862,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F144" s="5" t="str">
-        <v>16.3ms</v>
+        <v>47.9ms</v>
       </c>
       <c r="G144" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H144" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 16.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 47.9ms. Payload matches schema.</v>
       </c>
       <c r="I144" s="5" t="str">
         <v>PASS</v>
@@ -15894,13 +15894,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F145" s="5" t="str">
-        <v>49.6ms</v>
+        <v>51.8ms</v>
       </c>
       <c r="G145" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H145" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 49.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 51.8ms. Payload matches schema.</v>
       </c>
       <c r="I145" s="5" t="str">
         <v>PASS</v>
@@ -15926,13 +15926,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F146" s="5" t="str">
-        <v>43.8ms</v>
+        <v>41.2ms</v>
       </c>
       <c r="G146" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H146" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 43.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 41.2ms. Payload matches schema.</v>
       </c>
       <c r="I146" s="5" t="str">
         <v>PASS</v>
@@ -15958,13 +15958,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F147" s="5" t="str">
-        <v>57.6ms</v>
+        <v>10.2ms</v>
       </c>
       <c r="G147" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H147" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 57.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 10.2ms. Payload matches schema.</v>
       </c>
       <c r="I147" s="5" t="str">
         <v>PASS</v>
@@ -15990,13 +15990,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F148" s="5" t="str">
-        <v>16.3ms</v>
+        <v>50.0ms</v>
       </c>
       <c r="G148" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H148" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 16.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 50.0ms. Payload matches schema.</v>
       </c>
       <c r="I148" s="5" t="str">
         <v>PASS</v>
@@ -16022,13 +16022,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F149" s="5" t="str">
-        <v>28.5ms</v>
+        <v>20.0ms</v>
       </c>
       <c r="G149" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H149" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 28.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 20.0ms. Payload matches schema.</v>
       </c>
       <c r="I149" s="5" t="str">
         <v>PASS</v>
@@ -16054,13 +16054,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F150" s="5" t="str">
-        <v>21.7ms</v>
+        <v>59.3ms</v>
       </c>
       <c r="G150" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H150" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 21.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 59.3ms. Payload matches schema.</v>
       </c>
       <c r="I150" s="5" t="str">
         <v>PASS</v>
@@ -16086,13 +16086,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F151" s="5" t="str">
-        <v>18.7ms</v>
+        <v>18.9ms</v>
       </c>
       <c r="G151" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H151" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 18.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 18.9ms. Payload matches schema.</v>
       </c>
       <c r="I151" s="5" t="str">
         <v>PASS</v>
@@ -16118,13 +16118,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F152" s="5" t="str">
-        <v>53.9ms</v>
+        <v>41.0ms</v>
       </c>
       <c r="G152" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H152" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 53.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 41.0ms. Payload matches schema.</v>
       </c>
       <c r="I152" s="5" t="str">
         <v>PASS</v>
@@ -16150,13 +16150,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F153" s="5" t="str">
-        <v>29.3ms</v>
+        <v>25.2ms</v>
       </c>
       <c r="G153" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H153" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 29.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 25.2ms. Payload matches schema.</v>
       </c>
       <c r="I153" s="5" t="str">
         <v>PASS</v>
@@ -16182,13 +16182,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F154" s="5" t="str">
-        <v>35.2ms</v>
+        <v>14.4ms</v>
       </c>
       <c r="G154" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H154" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 35.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 14.4ms. Payload matches schema.</v>
       </c>
       <c r="I154" s="5" t="str">
         <v>PASS</v>
@@ -16214,13 +16214,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F155" s="5" t="str">
-        <v>54.1ms</v>
+        <v>42.2ms</v>
       </c>
       <c r="G155" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H155" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 54.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 42.2ms. Payload matches schema.</v>
       </c>
       <c r="I155" s="5" t="str">
         <v>PASS</v>
@@ -16246,13 +16246,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F156" s="5" t="str">
-        <v>54.9ms</v>
+        <v>15.7ms</v>
       </c>
       <c r="G156" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H156" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 54.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 15.7ms. Payload matches schema.</v>
       </c>
       <c r="I156" s="5" t="str">
         <v>PASS</v>
@@ -16278,13 +16278,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F157" s="5" t="str">
-        <v>30.0ms</v>
+        <v>11.5ms</v>
       </c>
       <c r="G157" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H157" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 30.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 11.5ms. Payload matches schema.</v>
       </c>
       <c r="I157" s="5" t="str">
         <v>PASS</v>
@@ -16310,13 +16310,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F158" s="5" t="str">
-        <v>53.2ms</v>
+        <v>21.6ms</v>
       </c>
       <c r="G158" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H158" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 53.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 21.6ms. Payload matches schema.</v>
       </c>
       <c r="I158" s="5" t="str">
         <v>PASS</v>
@@ -16342,13 +16342,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F159" s="5" t="str">
-        <v>22.7ms</v>
+        <v>58.7ms</v>
       </c>
       <c r="G159" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H159" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 22.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 58.7ms. Payload matches schema.</v>
       </c>
       <c r="I159" s="5" t="str">
         <v>PASS</v>
@@ -16374,13 +16374,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F160" s="5" t="str">
-        <v>43.3ms</v>
+        <v>12.4ms</v>
       </c>
       <c r="G160" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H160" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 43.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 12.4ms. Payload matches schema.</v>
       </c>
       <c r="I160" s="5" t="str">
         <v>PASS</v>
@@ -16406,13 +16406,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F161" s="5" t="str">
-        <v>19.1ms</v>
+        <v>23.5ms</v>
       </c>
       <c r="G161" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H161" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 19.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 23.5ms. Payload matches schema.</v>
       </c>
       <c r="I161" s="5" t="str">
         <v>PASS</v>
@@ -16438,13 +16438,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F162" s="5" t="str">
-        <v>21.3ms</v>
+        <v>24.2ms</v>
       </c>
       <c r="G162" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H162" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 21.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 24.2ms. Payload matches schema.</v>
       </c>
       <c r="I162" s="5" t="str">
         <v>PASS</v>
@@ -16470,13 +16470,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F163" s="5" t="str">
-        <v>35.5ms</v>
+        <v>40.5ms</v>
       </c>
       <c r="G163" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H163" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 35.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 40.5ms. Payload matches schema.</v>
       </c>
       <c r="I163" s="5" t="str">
         <v>PASS</v>
@@ -16502,13 +16502,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F164" s="5" t="str">
-        <v>12.7ms</v>
+        <v>28.3ms</v>
       </c>
       <c r="G164" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H164" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 12.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 28.3ms. Payload matches schema.</v>
       </c>
       <c r="I164" s="5" t="str">
         <v>PASS</v>
@@ -16534,13 +16534,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F165" s="5" t="str">
-        <v>53.6ms</v>
+        <v>31.7ms</v>
       </c>
       <c r="G165" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H165" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 53.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 31.7ms. Payload matches schema.</v>
       </c>
       <c r="I165" s="5" t="str">
         <v>PASS</v>
@@ -16566,13 +16566,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F166" s="5" t="str">
-        <v>53.8ms</v>
+        <v>45.4ms</v>
       </c>
       <c r="G166" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H166" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 53.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 45.4ms. Payload matches schema.</v>
       </c>
       <c r="I166" s="5" t="str">
         <v>PASS</v>
@@ -16598,13 +16598,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F167" s="5" t="str">
-        <v>12.6ms</v>
+        <v>22.9ms</v>
       </c>
       <c r="G167" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H167" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 12.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 22.9ms. Payload matches schema.</v>
       </c>
       <c r="I167" s="5" t="str">
         <v>PASS</v>
@@ -16630,13 +16630,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F168" s="5" t="str">
-        <v>24.9ms</v>
+        <v>52.1ms</v>
       </c>
       <c r="G168" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H168" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 24.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 52.1ms. Payload matches schema.</v>
       </c>
       <c r="I168" s="5" t="str">
         <v>PASS</v>
@@ -16662,13 +16662,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F169" s="5" t="str">
-        <v>36.8ms</v>
+        <v>16.6ms</v>
       </c>
       <c r="G169" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H169" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 36.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 16.6ms. Payload matches schema.</v>
       </c>
       <c r="I169" s="5" t="str">
         <v>PASS</v>
@@ -16694,13 +16694,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F170" s="5" t="str">
-        <v>33.5ms</v>
+        <v>43.0ms</v>
       </c>
       <c r="G170" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H170" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 33.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 43.0ms. Payload matches schema.</v>
       </c>
       <c r="I170" s="5" t="str">
         <v>PASS</v>
@@ -16726,13 +16726,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F171" s="5" t="str">
-        <v>19.5ms</v>
+        <v>41.4ms</v>
       </c>
       <c r="G171" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H171" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 19.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 41.4ms. Payload matches schema.</v>
       </c>
       <c r="I171" s="5" t="str">
         <v>PASS</v>
@@ -16758,13 +16758,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F172" s="5" t="str">
-        <v>56.6ms</v>
+        <v>16.5ms</v>
       </c>
       <c r="G172" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H172" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 56.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 16.5ms. Payload matches schema.</v>
       </c>
       <c r="I172" s="5" t="str">
         <v>PASS</v>
@@ -16790,13 +16790,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F173" s="5" t="str">
-        <v>53.6ms</v>
+        <v>27.0ms</v>
       </c>
       <c r="G173" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H173" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 53.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 27.0ms. Payload matches schema.</v>
       </c>
       <c r="I173" s="5" t="str">
         <v>PASS</v>
@@ -16822,13 +16822,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F174" s="5" t="str">
-        <v>15.0ms</v>
+        <v>29.1ms</v>
       </c>
       <c r="G174" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H174" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 15.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 29.1ms. Payload matches schema.</v>
       </c>
       <c r="I174" s="5" t="str">
         <v>PASS</v>
@@ -16854,13 +16854,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F175" s="5" t="str">
-        <v>58.4ms</v>
+        <v>49.3ms</v>
       </c>
       <c r="G175" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H175" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 58.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 49.3ms. Payload matches schema.</v>
       </c>
       <c r="I175" s="5" t="str">
         <v>PASS</v>
@@ -16886,13 +16886,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F176" s="5" t="str">
-        <v>58.0ms</v>
+        <v>41.4ms</v>
       </c>
       <c r="G176" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H176" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 58.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 41.4ms. Payload matches schema.</v>
       </c>
       <c r="I176" s="5" t="str">
         <v>PASS</v>
@@ -16918,13 +16918,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F177" s="5" t="str">
-        <v>29.1ms</v>
+        <v>48.9ms</v>
       </c>
       <c r="G177" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H177" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 29.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 48.9ms. Payload matches schema.</v>
       </c>
       <c r="I177" s="5" t="str">
         <v>PASS</v>
@@ -16950,13 +16950,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F178" s="5" t="str">
-        <v>59.5ms</v>
+        <v>55.9ms</v>
       </c>
       <c r="G178" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H178" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 59.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 55.9ms. Payload matches schema.</v>
       </c>
       <c r="I178" s="5" t="str">
         <v>PASS</v>
@@ -16982,13 +16982,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F179" s="5" t="str">
-        <v>28.6ms</v>
+        <v>11.8ms</v>
       </c>
       <c r="G179" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H179" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 28.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 11.8ms. Payload matches schema.</v>
       </c>
       <c r="I179" s="5" t="str">
         <v>PASS</v>
@@ -17014,13 +17014,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F180" s="5" t="str">
-        <v>14.7ms</v>
+        <v>41.7ms</v>
       </c>
       <c r="G180" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H180" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 14.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 41.7ms. Payload matches schema.</v>
       </c>
       <c r="I180" s="5" t="str">
         <v>PASS</v>
@@ -17046,13 +17046,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F181" s="5" t="str">
-        <v>16.4ms</v>
+        <v>11.3ms</v>
       </c>
       <c r="G181" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H181" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 16.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 11.3ms. Payload matches schema.</v>
       </c>
       <c r="I181" s="5" t="str">
         <v>PASS</v>
@@ -17078,13 +17078,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F182" s="5" t="str">
-        <v>55.4ms</v>
+        <v>43.1ms</v>
       </c>
       <c r="G182" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H182" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 55.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 43.1ms. Payload matches schema.</v>
       </c>
       <c r="I182" s="5" t="str">
         <v>PASS</v>
@@ -17110,13 +17110,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F183" s="5" t="str">
-        <v>43.5ms</v>
+        <v>17.9ms</v>
       </c>
       <c r="G183" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H183" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 43.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 17.9ms. Payload matches schema.</v>
       </c>
       <c r="I183" s="5" t="str">
         <v>PASS</v>
@@ -17142,13 +17142,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F184" s="5" t="str">
-        <v>36.1ms</v>
+        <v>58.4ms</v>
       </c>
       <c r="G184" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H184" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 36.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 58.4ms. Payload matches schema.</v>
       </c>
       <c r="I184" s="5" t="str">
         <v>PASS</v>
@@ -17174,13 +17174,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F185" s="5" t="str">
-        <v>45.0ms</v>
+        <v>50.1ms</v>
       </c>
       <c r="G185" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H185" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 45.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 50.1ms. Payload matches schema.</v>
       </c>
       <c r="I185" s="5" t="str">
         <v>PASS</v>
@@ -17206,13 +17206,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F186" s="5" t="str">
-        <v>24.1ms</v>
+        <v>20.5ms</v>
       </c>
       <c r="G186" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H186" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 24.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 20.5ms. Payload matches schema.</v>
       </c>
       <c r="I186" s="5" t="str">
         <v>PASS</v>
@@ -17238,13 +17238,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F187" s="5" t="str">
-        <v>39.5ms</v>
+        <v>24.4ms</v>
       </c>
       <c r="G187" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H187" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 39.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 24.4ms. Payload matches schema.</v>
       </c>
       <c r="I187" s="5" t="str">
         <v>PASS</v>
@@ -17270,13 +17270,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F188" s="5" t="str">
-        <v>29.7ms</v>
+        <v>49.3ms</v>
       </c>
       <c r="G188" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H188" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 29.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 49.3ms. Payload matches schema.</v>
       </c>
       <c r="I188" s="5" t="str">
         <v>PASS</v>
@@ -17302,13 +17302,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F189" s="5" t="str">
-        <v>38.4ms</v>
+        <v>38.5ms</v>
       </c>
       <c r="G189" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H189" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 38.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 38.5ms. Payload matches schema.</v>
       </c>
       <c r="I189" s="5" t="str">
         <v>PASS</v>
@@ -17334,13 +17334,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F190" s="5" t="str">
-        <v>37.0ms</v>
+        <v>47.3ms</v>
       </c>
       <c r="G190" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H190" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 37.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 47.3ms. Payload matches schema.</v>
       </c>
       <c r="I190" s="5" t="str">
         <v>PASS</v>
@@ -17366,13 +17366,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F191" s="5" t="str">
-        <v>13.8ms</v>
+        <v>35.1ms</v>
       </c>
       <c r="G191" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H191" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 13.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 35.1ms. Payload matches schema.</v>
       </c>
       <c r="I191" s="5" t="str">
         <v>PASS</v>
@@ -17398,13 +17398,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F192" s="5" t="str">
-        <v>20.1ms</v>
+        <v>30.2ms</v>
       </c>
       <c r="G192" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H192" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 20.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 30.2ms. Payload matches schema.</v>
       </c>
       <c r="I192" s="5" t="str">
         <v>PASS</v>
@@ -17430,13 +17430,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F193" s="5" t="str">
-        <v>20.8ms</v>
+        <v>55.4ms</v>
       </c>
       <c r="G193" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H193" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 20.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 55.4ms. Payload matches schema.</v>
       </c>
       <c r="I193" s="5" t="str">
         <v>PASS</v>
@@ -17462,13 +17462,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F194" s="5" t="str">
-        <v>53.9ms</v>
+        <v>23.3ms</v>
       </c>
       <c r="G194" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H194" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 53.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 23.3ms. Payload matches schema.</v>
       </c>
       <c r="I194" s="5" t="str">
         <v>PASS</v>
@@ -17494,13 +17494,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F195" s="5" t="str">
-        <v>34.0ms</v>
+        <v>40.0ms</v>
       </c>
       <c r="G195" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H195" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 34.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 40.0ms. Payload matches schema.</v>
       </c>
       <c r="I195" s="5" t="str">
         <v>PASS</v>
@@ -17526,13 +17526,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F196" s="5" t="str">
-        <v>57.6ms</v>
+        <v>12.2ms</v>
       </c>
       <c r="G196" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H196" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 57.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 12.2ms. Payload matches schema.</v>
       </c>
       <c r="I196" s="5" t="str">
         <v>PASS</v>
@@ -17558,13 +17558,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F197" s="5" t="str">
-        <v>36.0ms</v>
+        <v>53.4ms</v>
       </c>
       <c r="G197" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H197" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 36.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 53.4ms. Payload matches schema.</v>
       </c>
       <c r="I197" s="5" t="str">
         <v>PASS</v>
@@ -17590,13 +17590,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F198" s="5" t="str">
-        <v>49.2ms</v>
+        <v>47.3ms</v>
       </c>
       <c r="G198" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H198" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 49.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 47.3ms. Payload matches schema.</v>
       </c>
       <c r="I198" s="5" t="str">
         <v>PASS</v>
@@ -17622,13 +17622,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F199" s="5" t="str">
-        <v>58.6ms</v>
+        <v>19.3ms</v>
       </c>
       <c r="G199" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H199" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 58.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 19.3ms. Payload matches schema.</v>
       </c>
       <c r="I199" s="5" t="str">
         <v>PASS</v>
@@ -17654,13 +17654,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F200" s="5" t="str">
-        <v>52.7ms</v>
+        <v>44.5ms</v>
       </c>
       <c r="G200" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H200" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 52.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 44.5ms. Payload matches schema.</v>
       </c>
       <c r="I200" s="5" t="str">
         <v>PASS</v>
@@ -17686,13 +17686,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F201" s="5" t="str">
-        <v>33.4ms</v>
+        <v>13.4ms</v>
       </c>
       <c r="G201" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H201" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 33.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 13.4ms. Payload matches schema.</v>
       </c>
       <c r="I201" s="5" t="str">
         <v>PASS</v>
@@ -17718,13 +17718,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F202" s="5" t="str">
-        <v>32.4ms</v>
+        <v>42.7ms</v>
       </c>
       <c r="G202" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H202" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 32.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 42.7ms. Payload matches schema.</v>
       </c>
       <c r="I202" s="5" t="str">
         <v>PASS</v>
@@ -17750,13 +17750,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F203" s="5" t="str">
-        <v>59.3ms</v>
+        <v>25.7ms</v>
       </c>
       <c r="G203" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H203" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 59.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 25.7ms. Payload matches schema.</v>
       </c>
       <c r="I203" s="5" t="str">
         <v>PASS</v>
@@ -17782,13 +17782,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F204" s="5" t="str">
-        <v>24.9ms</v>
+        <v>27.1ms</v>
       </c>
       <c r="G204" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H204" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 24.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 27.1ms. Payload matches schema.</v>
       </c>
       <c r="I204" s="5" t="str">
         <v>PASS</v>
@@ -17814,13 +17814,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F205" s="5" t="str">
-        <v>45.3ms</v>
+        <v>35.2ms</v>
       </c>
       <c r="G205" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H205" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 45.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 35.2ms. Payload matches schema.</v>
       </c>
       <c r="I205" s="5" t="str">
         <v>PASS</v>
@@ -17846,13 +17846,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F206" s="5" t="str">
-        <v>16.2ms</v>
+        <v>34.6ms</v>
       </c>
       <c r="G206" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H206" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 16.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 34.6ms. Payload matches schema.</v>
       </c>
       <c r="I206" s="5" t="str">
         <v>PASS</v>
@@ -17878,13 +17878,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F207" s="5" t="str">
-        <v>44.6ms</v>
+        <v>28.5ms</v>
       </c>
       <c r="G207" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H207" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 44.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 28.5ms. Payload matches schema.</v>
       </c>
       <c r="I207" s="5" t="str">
         <v>PASS</v>
@@ -17910,13 +17910,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F208" s="5" t="str">
-        <v>46.3ms</v>
+        <v>36.0ms</v>
       </c>
       <c r="G208" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H208" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 46.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 36.0ms. Payload matches schema.</v>
       </c>
       <c r="I208" s="5" t="str">
         <v>PASS</v>
@@ -17942,13 +17942,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F209" s="5" t="str">
-        <v>55.6ms</v>
+        <v>26.0ms</v>
       </c>
       <c r="G209" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H209" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 55.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 26.0ms. Payload matches schema.</v>
       </c>
       <c r="I209" s="5" t="str">
         <v>PASS</v>
@@ -17974,13 +17974,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F210" s="5" t="str">
-        <v>57.0ms</v>
+        <v>44.5ms</v>
       </c>
       <c r="G210" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H210" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 57.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 44.5ms. Payload matches schema.</v>
       </c>
       <c r="I210" s="5" t="str">
         <v>PASS</v>
@@ -18006,13 +18006,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F211" s="5" t="str">
-        <v>59.9ms</v>
+        <v>47.5ms</v>
       </c>
       <c r="G211" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H211" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 59.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 47.5ms. Payload matches schema.</v>
       </c>
       <c r="I211" s="5" t="str">
         <v>PASS</v>
@@ -18038,13 +18038,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F212" s="5" t="str">
-        <v>47.8ms</v>
+        <v>43.5ms</v>
       </c>
       <c r="G212" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H212" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 47.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 43.5ms. Payload matches schema.</v>
       </c>
       <c r="I212" s="5" t="str">
         <v>PASS</v>
@@ -18070,13 +18070,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F213" s="5" t="str">
-        <v>45.3ms</v>
+        <v>32.6ms</v>
       </c>
       <c r="G213" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H213" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 45.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 32.6ms. Payload matches schema.</v>
       </c>
       <c r="I213" s="5" t="str">
         <v>PASS</v>
@@ -18102,13 +18102,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F214" s="5" t="str">
-        <v>49.2ms</v>
+        <v>25.5ms</v>
       </c>
       <c r="G214" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H214" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 49.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 25.5ms. Payload matches schema.</v>
       </c>
       <c r="I214" s="5" t="str">
         <v>PASS</v>
@@ -18134,13 +18134,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F215" s="5" t="str">
-        <v>21.2ms</v>
+        <v>58.4ms</v>
       </c>
       <c r="G215" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H215" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 21.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 58.4ms. Payload matches schema.</v>
       </c>
       <c r="I215" s="5" t="str">
         <v>PASS</v>
@@ -18166,13 +18166,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F216" s="5" t="str">
-        <v>49.9ms</v>
+        <v>14.2ms</v>
       </c>
       <c r="G216" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H216" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 49.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 14.2ms. Payload matches schema.</v>
       </c>
       <c r="I216" s="5" t="str">
         <v>PASS</v>
@@ -18198,13 +18198,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F217" s="5" t="str">
-        <v>12.7ms</v>
+        <v>36.8ms</v>
       </c>
       <c r="G217" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H217" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 12.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 36.8ms. Payload matches schema.</v>
       </c>
       <c r="I217" s="5" t="str">
         <v>PASS</v>
@@ -18230,13 +18230,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F218" s="5" t="str">
-        <v>31.7ms</v>
+        <v>57.1ms</v>
       </c>
       <c r="G218" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H218" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 31.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 57.1ms. Payload matches schema.</v>
       </c>
       <c r="I218" s="5" t="str">
         <v>PASS</v>
@@ -18262,13 +18262,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F219" s="5" t="str">
-        <v>31.5ms</v>
+        <v>23.8ms</v>
       </c>
       <c r="G219" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H219" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 31.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 23.8ms. Payload matches schema.</v>
       </c>
       <c r="I219" s="5" t="str">
         <v>PASS</v>
@@ -18294,13 +18294,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F220" s="5" t="str">
-        <v>33.8ms</v>
+        <v>32.1ms</v>
       </c>
       <c r="G220" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H220" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 33.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 32.1ms. Payload matches schema.</v>
       </c>
       <c r="I220" s="5" t="str">
         <v>PASS</v>
@@ -18326,13 +18326,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F221" s="5" t="str">
-        <v>36.3ms</v>
+        <v>44.4ms</v>
       </c>
       <c r="G221" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H221" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 36.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 44.4ms. Payload matches schema.</v>
       </c>
       <c r="I221" s="5" t="str">
         <v>PASS</v>
@@ -18358,13 +18358,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F222" s="5" t="str">
-        <v>35.6ms</v>
+        <v>44.2ms</v>
       </c>
       <c r="G222" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H222" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 35.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 44.2ms. Payload matches schema.</v>
       </c>
       <c r="I222" s="5" t="str">
         <v>PASS</v>
@@ -18390,13 +18390,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F223" s="5" t="str">
-        <v>13.9ms</v>
+        <v>38.1ms</v>
       </c>
       <c r="G223" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H223" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 13.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 38.1ms. Payload matches schema.</v>
       </c>
       <c r="I223" s="5" t="str">
         <v>PASS</v>
@@ -18422,13 +18422,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F224" s="5" t="str">
-        <v>16.5ms</v>
+        <v>42.6ms</v>
       </c>
       <c r="G224" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H224" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 16.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 42.6ms. Payload matches schema.</v>
       </c>
       <c r="I224" s="5" t="str">
         <v>PASS</v>
@@ -18454,13 +18454,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F225" s="5" t="str">
-        <v>50.5ms</v>
+        <v>31.6ms</v>
       </c>
       <c r="G225" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H225" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 50.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 31.6ms. Payload matches schema.</v>
       </c>
       <c r="I225" s="5" t="str">
         <v>PASS</v>
@@ -18486,13 +18486,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F226" s="5" t="str">
-        <v>56.9ms</v>
+        <v>34.2ms</v>
       </c>
       <c r="G226" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H226" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 56.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 34.2ms. Payload matches schema.</v>
       </c>
       <c r="I226" s="5" t="str">
         <v>PASS</v>
@@ -18518,13 +18518,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F227" s="5" t="str">
-        <v>52.9ms</v>
+        <v>31.4ms</v>
       </c>
       <c r="G227" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H227" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 52.9ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 31.4ms. Payload matches schema.</v>
       </c>
       <c r="I227" s="5" t="str">
         <v>PASS</v>
@@ -18550,13 +18550,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F228" s="5" t="str">
-        <v>23.3ms</v>
+        <v>56.0ms</v>
       </c>
       <c r="G228" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H228" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 23.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 56.0ms. Payload matches schema.</v>
       </c>
       <c r="I228" s="5" t="str">
         <v>PASS</v>
@@ -18582,13 +18582,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F229" s="5" t="str">
-        <v>12.7ms</v>
+        <v>50.9ms</v>
       </c>
       <c r="G229" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H229" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 12.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 50.9ms. Payload matches schema.</v>
       </c>
       <c r="I229" s="5" t="str">
         <v>PASS</v>
@@ -18614,13 +18614,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F230" s="5" t="str">
-        <v>22.8ms</v>
+        <v>15.2ms</v>
       </c>
       <c r="G230" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H230" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 22.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 15.2ms. Payload matches schema.</v>
       </c>
       <c r="I230" s="5" t="str">
         <v>PASS</v>
@@ -18646,13 +18646,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F231" s="5" t="str">
-        <v>14.0ms</v>
+        <v>50.1ms</v>
       </c>
       <c r="G231" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H231" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 14.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 50.1ms. Payload matches schema.</v>
       </c>
       <c r="I231" s="5" t="str">
         <v>PASS</v>
@@ -18678,13 +18678,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F232" s="5" t="str">
-        <v>56.1ms</v>
+        <v>19.4ms</v>
       </c>
       <c r="G232" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H232" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 56.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 19.4ms. Payload matches schema.</v>
       </c>
       <c r="I232" s="5" t="str">
         <v>PASS</v>
@@ -18710,13 +18710,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F233" s="5" t="str">
-        <v>57.1ms</v>
+        <v>27.2ms</v>
       </c>
       <c r="G233" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H233" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 57.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 27.2ms. Payload matches schema.</v>
       </c>
       <c r="I233" s="5" t="str">
         <v>PASS</v>
@@ -18742,13 +18742,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F234" s="5" t="str">
-        <v>37.0ms</v>
+        <v>10.1ms</v>
       </c>
       <c r="G234" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H234" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 37.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 10.1ms. Payload matches schema.</v>
       </c>
       <c r="I234" s="5" t="str">
         <v>PASS</v>
@@ -18774,13 +18774,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F235" s="5" t="str">
-        <v>15.6ms</v>
+        <v>43.5ms</v>
       </c>
       <c r="G235" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H235" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 15.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 43.5ms. Payload matches schema.</v>
       </c>
       <c r="I235" s="5" t="str">
         <v>PASS</v>
@@ -18806,13 +18806,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F236" s="5" t="str">
-        <v>32.2ms</v>
+        <v>56.7ms</v>
       </c>
       <c r="G236" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H236" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 32.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 56.7ms. Payload matches schema.</v>
       </c>
       <c r="I236" s="5" t="str">
         <v>PASS</v>
@@ -18838,13 +18838,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F237" s="5" t="str">
-        <v>13.4ms</v>
+        <v>50.9ms</v>
       </c>
       <c r="G237" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H237" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 13.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 50.9ms. Payload matches schema.</v>
       </c>
       <c r="I237" s="5" t="str">
         <v>PASS</v>
@@ -18870,13 +18870,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F238" s="5" t="str">
-        <v>49.7ms</v>
+        <v>49.5ms</v>
       </c>
       <c r="G238" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H238" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 49.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 49.5ms. Payload matches schema.</v>
       </c>
       <c r="I238" s="5" t="str">
         <v>PASS</v>
@@ -18902,13 +18902,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F239" s="5" t="str">
-        <v>59.4ms</v>
+        <v>18.9ms</v>
       </c>
       <c r="G239" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H239" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 59.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 18.9ms. Payload matches schema.</v>
       </c>
       <c r="I239" s="5" t="str">
         <v>PASS</v>
@@ -18934,13 +18934,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F240" s="5" t="str">
-        <v>50.0ms</v>
+        <v>13.7ms</v>
       </c>
       <c r="G240" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H240" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 50.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 13.7ms. Payload matches schema.</v>
       </c>
       <c r="I240" s="5" t="str">
         <v>PASS</v>
@@ -18966,13 +18966,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F241" s="5" t="str">
-        <v>46.1ms</v>
+        <v>39.8ms</v>
       </c>
       <c r="G241" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H241" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 46.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 39.8ms. Payload matches schema.</v>
       </c>
       <c r="I241" s="5" t="str">
         <v>PASS</v>
@@ -19030,13 +19030,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F243" s="5" t="str">
-        <v>43.7ms</v>
+        <v>58.0ms</v>
       </c>
       <c r="G243" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H243" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 43.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 58.0ms. Payload matches schema.</v>
       </c>
       <c r="I243" s="5" t="str">
         <v>PASS</v>
@@ -19062,13 +19062,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F244" s="5" t="str">
-        <v>55.3ms</v>
+        <v>32.4ms</v>
       </c>
       <c r="G244" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H244" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 55.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 32.4ms. Payload matches schema.</v>
       </c>
       <c r="I244" s="5" t="str">
         <v>PASS</v>
@@ -19094,13 +19094,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F245" s="5" t="str">
-        <v>44.5ms</v>
+        <v>13.6ms</v>
       </c>
       <c r="G245" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H245" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 44.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 13.6ms. Payload matches schema.</v>
       </c>
       <c r="I245" s="5" t="str">
         <v>PASS</v>
@@ -19126,13 +19126,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F246" s="5" t="str">
-        <v>53.2ms</v>
+        <v>34.3ms</v>
       </c>
       <c r="G246" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H246" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 53.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 34.3ms. Payload matches schema.</v>
       </c>
       <c r="I246" s="5" t="str">
         <v>PASS</v>
@@ -19158,13 +19158,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F247" s="5" t="str">
-        <v>31.7ms</v>
+        <v>51.8ms</v>
       </c>
       <c r="G247" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H247" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 31.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 51.8ms. Payload matches schema.</v>
       </c>
       <c r="I247" s="5" t="str">
         <v>PASS</v>
@@ -19190,13 +19190,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F248" s="5" t="str">
-        <v>21.0ms</v>
+        <v>26.6ms</v>
       </c>
       <c r="G248" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H248" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 21.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 26.6ms. Payload matches schema.</v>
       </c>
       <c r="I248" s="5" t="str">
         <v>PASS</v>
@@ -19222,13 +19222,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F249" s="5" t="str">
-        <v>32.1ms</v>
+        <v>32.6ms</v>
       </c>
       <c r="G249" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H249" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 32.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 32.6ms. Payload matches schema.</v>
       </c>
       <c r="I249" s="5" t="str">
         <v>PASS</v>
@@ -19254,13 +19254,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F250" s="5" t="str">
-        <v>11.4ms</v>
+        <v>56.7ms</v>
       </c>
       <c r="G250" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H250" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 11.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 56.7ms. Payload matches schema.</v>
       </c>
       <c r="I250" s="5" t="str">
         <v>PASS</v>
@@ -19286,13 +19286,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F251" s="5" t="str">
-        <v>20.0ms</v>
+        <v>49.8ms</v>
       </c>
       <c r="G251" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H251" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 20.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 49.8ms. Payload matches schema.</v>
       </c>
       <c r="I251" s="5" t="str">
         <v>PASS</v>
@@ -19318,13 +19318,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F252" s="5" t="str">
-        <v>11.5ms</v>
+        <v>26.6ms</v>
       </c>
       <c r="G252" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H252" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 11.5ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 26.6ms. Payload matches schema.</v>
       </c>
       <c r="I252" s="5" t="str">
         <v>PASS</v>
@@ -19350,13 +19350,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F253" s="5" t="str">
-        <v>32.7ms</v>
+        <v>34.7ms</v>
       </c>
       <c r="G253" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H253" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 32.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 34.7ms. Payload matches schema.</v>
       </c>
       <c r="I253" s="5" t="str">
         <v>PASS</v>
@@ -19382,13 +19382,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F254" s="5" t="str">
-        <v>44.7ms</v>
+        <v>40.6ms</v>
       </c>
       <c r="G254" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H254" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 44.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 40.6ms. Payload matches schema.</v>
       </c>
       <c r="I254" s="5" t="str">
         <v>PASS</v>
@@ -19414,13 +19414,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F255" s="5" t="str">
-        <v>40.3ms</v>
+        <v>33.9ms</v>
       </c>
       <c r="G255" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H255" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 40.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 33.9ms. Payload matches schema.</v>
       </c>
       <c r="I255" s="5" t="str">
         <v>PASS</v>
@@ -19446,13 +19446,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F256" s="5" t="str">
-        <v>43.8ms</v>
+        <v>55.0ms</v>
       </c>
       <c r="G256" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H256" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 43.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 55.0ms. Payload matches schema.</v>
       </c>
       <c r="I256" s="5" t="str">
         <v>PASS</v>
@@ -19478,13 +19478,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F257" s="5" t="str">
-        <v>50.8ms</v>
+        <v>29.7ms</v>
       </c>
       <c r="G257" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H257" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 50.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 29.7ms. Payload matches schema.</v>
       </c>
       <c r="I257" s="5" t="str">
         <v>PASS</v>
@@ -19510,13 +19510,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F258" s="5" t="str">
-        <v>54.4ms</v>
+        <v>43.1ms</v>
       </c>
       <c r="G258" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H258" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 54.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 43.1ms. Payload matches schema.</v>
       </c>
       <c r="I258" s="5" t="str">
         <v>PASS</v>
@@ -19542,13 +19542,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F259" s="5" t="str">
-        <v>42.1ms</v>
+        <v>59.9ms</v>
       </c>
       <c r="G259" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H259" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 42.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 59.9ms. Payload matches schema.</v>
       </c>
       <c r="I259" s="5" t="str">
         <v>PASS</v>
@@ -19574,13 +19574,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F260" s="5" t="str">
-        <v>19.4ms</v>
+        <v>17.7ms</v>
       </c>
       <c r="G260" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H260" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 19.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 17.7ms. Payload matches schema.</v>
       </c>
       <c r="I260" s="5" t="str">
         <v>PASS</v>
@@ -19606,13 +19606,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F261" s="5" t="str">
-        <v>43.3ms</v>
+        <v>49.0ms</v>
       </c>
       <c r="G261" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H261" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 43.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 49.0ms. Payload matches schema.</v>
       </c>
       <c r="I261" s="5" t="str">
         <v>PASS</v>
@@ -19638,13 +19638,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F262" s="5" t="str">
-        <v>56.0ms</v>
+        <v>22.8ms</v>
       </c>
       <c r="G262" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H262" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 56.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 22.8ms. Payload matches schema.</v>
       </c>
       <c r="I262" s="5" t="str">
         <v>PASS</v>
@@ -19670,13 +19670,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F263" s="5" t="str">
-        <v>33.5ms</v>
+        <v>42.2ms</v>
       </c>
       <c r="G263" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H263" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 33.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 42.2ms. Payload matches schema.</v>
       </c>
       <c r="I263" s="5" t="str">
         <v>PASS</v>
@@ -19702,13 +19702,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F264" s="5" t="str">
-        <v>56.4ms</v>
+        <v>28.1ms</v>
       </c>
       <c r="G264" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H264" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 56.4ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 28.1ms. Payload matches schema.</v>
       </c>
       <c r="I264" s="5" t="str">
         <v>PASS</v>
@@ -19734,13 +19734,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F265" s="5" t="str">
-        <v>47.1ms</v>
+        <v>59.2ms</v>
       </c>
       <c r="G265" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H265" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 47.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 59.2ms. Payload matches schema.</v>
       </c>
       <c r="I265" s="5" t="str">
         <v>PASS</v>
@@ -19766,13 +19766,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F266" s="5" t="str">
-        <v>10.6ms</v>
+        <v>50.6ms</v>
       </c>
       <c r="G266" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H266" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 10.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 50.6ms. Payload matches schema.</v>
       </c>
       <c r="I266" s="5" t="str">
         <v>PASS</v>
@@ -19798,13 +19798,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F267" s="5" t="str">
-        <v>18.3ms</v>
+        <v>48.1ms</v>
       </c>
       <c r="G267" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H267" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 18.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 48.1ms. Payload matches schema.</v>
       </c>
       <c r="I267" s="5" t="str">
         <v>PASS</v>
@@ -19830,13 +19830,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F268" s="5" t="str">
-        <v>13.1ms</v>
+        <v>24.7ms</v>
       </c>
       <c r="G268" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H268" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 13.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 24.7ms. Payload matches schema.</v>
       </c>
       <c r="I268" s="5" t="str">
         <v>PASS</v>
@@ -19862,13 +19862,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F269" s="5" t="str">
-        <v>47.0ms</v>
+        <v>17.3ms</v>
       </c>
       <c r="G269" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H269" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 47.0ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 17.3ms. Payload matches schema.</v>
       </c>
       <c r="I269" s="5" t="str">
         <v>PASS</v>
@@ -19894,13 +19894,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F270" s="5" t="str">
-        <v>18.2ms</v>
+        <v>35.3ms</v>
       </c>
       <c r="G270" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H270" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 18.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 35.3ms. Payload matches schema.</v>
       </c>
       <c r="I270" s="5" t="str">
         <v>PASS</v>
@@ -19926,13 +19926,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F271" s="5" t="str">
-        <v>48.2ms</v>
+        <v>34.2ms</v>
       </c>
       <c r="G271" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H271" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 48.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 34.2ms. Payload matches schema.</v>
       </c>
       <c r="I271" s="5" t="str">
         <v>PASS</v>
@@ -19958,13 +19958,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F272" s="5" t="str">
-        <v>37.8ms</v>
+        <v>43.1ms</v>
       </c>
       <c r="G272" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H272" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 37.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 43.1ms. Payload matches schema.</v>
       </c>
       <c r="I272" s="5" t="str">
         <v>PASS</v>
@@ -19990,13 +19990,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F273" s="5" t="str">
-        <v>30.8ms</v>
+        <v>40.9ms</v>
       </c>
       <c r="G273" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H273" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 30.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 40.9ms. Payload matches schema.</v>
       </c>
       <c r="I273" s="5" t="str">
         <v>PASS</v>
@@ -20022,13 +20022,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F274" s="5" t="str">
-        <v>54.7ms</v>
+        <v>47.9ms</v>
       </c>
       <c r="G274" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H274" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 54.7ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 47.9ms. Payload matches schema.</v>
       </c>
       <c r="I274" s="5" t="str">
         <v>PASS</v>
@@ -20054,13 +20054,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F275" s="5" t="str">
-        <v>56.5ms</v>
+        <v>34.9ms</v>
       </c>
       <c r="G275" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H275" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 56.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 34.9ms. Payload matches schema.</v>
       </c>
       <c r="I275" s="5" t="str">
         <v>PASS</v>
@@ -20086,13 +20086,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F276" s="5" t="str">
-        <v>49.5ms</v>
+        <v>38.6ms</v>
       </c>
       <c r="G276" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H276" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 49.5ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 38.6ms. Payload matches schema.</v>
       </c>
       <c r="I276" s="5" t="str">
         <v>PASS</v>
@@ -20118,13 +20118,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F277" s="5" t="str">
-        <v>26.1ms</v>
+        <v>26.5ms</v>
       </c>
       <c r="G277" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H277" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 26.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 26.5ms. Payload matches schema.</v>
       </c>
       <c r="I277" s="5" t="str">
         <v>PASS</v>
@@ -20150,13 +20150,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F278" s="5" t="str">
-        <v>42.9ms</v>
+        <v>26.6ms</v>
       </c>
       <c r="G278" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H278" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 42.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 26.6ms. Payload matches schema.</v>
       </c>
       <c r="I278" s="5" t="str">
         <v>PASS</v>
@@ -20182,13 +20182,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F279" s="5" t="str">
-        <v>34.6ms</v>
+        <v>33.0ms</v>
       </c>
       <c r="G279" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H279" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 34.6ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 33.0ms. Payload matches schema.</v>
       </c>
       <c r="I279" s="5" t="str">
         <v>PASS</v>
@@ -20214,13 +20214,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F280" s="5" t="str">
-        <v>35.3ms</v>
+        <v>56.0ms</v>
       </c>
       <c r="G280" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H280" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 35.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 56.0ms. Payload matches schema.</v>
       </c>
       <c r="I280" s="5" t="str">
         <v>PASS</v>
@@ -20246,13 +20246,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F281" s="5" t="str">
-        <v>34.6ms</v>
+        <v>45.2ms</v>
       </c>
       <c r="G281" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H281" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 34.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 45.2ms. Payload matches schema.</v>
       </c>
       <c r="I281" s="5" t="str">
         <v>PASS</v>
@@ -20278,13 +20278,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F282" s="5" t="str">
-        <v>49.6ms</v>
+        <v>35.5ms</v>
       </c>
       <c r="G282" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H282" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 49.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 35.5ms. Payload matches schema.</v>
       </c>
       <c r="I282" s="5" t="str">
         <v>PASS</v>
@@ -20310,13 +20310,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F283" s="5" t="str">
-        <v>36.1ms</v>
+        <v>31.9ms</v>
       </c>
       <c r="G283" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H283" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 36.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 31.9ms. Payload matches schema.</v>
       </c>
       <c r="I283" s="5" t="str">
         <v>PASS</v>
@@ -20342,13 +20342,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F284" s="5" t="str">
-        <v>45.8ms</v>
+        <v>15.5ms</v>
       </c>
       <c r="G284" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H284" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 45.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 15.5ms. Payload matches schema.</v>
       </c>
       <c r="I284" s="5" t="str">
         <v>PASS</v>
@@ -20374,13 +20374,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F285" s="5" t="str">
-        <v>22.9ms</v>
+        <v>18.3ms</v>
       </c>
       <c r="G285" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H285" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 22.9ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 18.3ms. Payload matches schema.</v>
       </c>
       <c r="I285" s="5" t="str">
         <v>PASS</v>
@@ -20406,13 +20406,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F286" s="5" t="str">
-        <v>56.3ms</v>
+        <v>33.3ms</v>
       </c>
       <c r="G286" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H286" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 56.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 33.3ms. Payload matches schema.</v>
       </c>
       <c r="I286" s="5" t="str">
         <v>PASS</v>
@@ -20438,13 +20438,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F287" s="5" t="str">
-        <v>31.2ms</v>
+        <v>17.9ms</v>
       </c>
       <c r="G287" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H287" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 31.2ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 17.9ms. Payload matches schema.</v>
       </c>
       <c r="I287" s="5" t="str">
         <v>PASS</v>
@@ -20470,13 +20470,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F288" s="5" t="str">
-        <v>32.7ms</v>
+        <v>12.2ms</v>
       </c>
       <c r="G288" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H288" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 32.7ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 12.2ms. Payload matches schema.</v>
       </c>
       <c r="I288" s="5" t="str">
         <v>PASS</v>
@@ -20502,13 +20502,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F289" s="5" t="str">
-        <v>41.4ms</v>
+        <v>59.1ms</v>
       </c>
       <c r="G289" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H289" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 41.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 59.1ms. Payload matches schema.</v>
       </c>
       <c r="I289" s="5" t="str">
         <v>PASS</v>
@@ -20534,13 +20534,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F290" s="5" t="str">
-        <v>51.8ms</v>
+        <v>51.4ms</v>
       </c>
       <c r="G290" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H290" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 51.8ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 51.4ms. Payload matches schema.</v>
       </c>
       <c r="I290" s="5" t="str">
         <v>PASS</v>
@@ -20566,13 +20566,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F291" s="5" t="str">
-        <v>35.1ms</v>
+        <v>37.6ms</v>
       </c>
       <c r="G291" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H291" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 35.1ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 37.6ms. Payload matches schema.</v>
       </c>
       <c r="I291" s="5" t="str">
         <v>PASS</v>
@@ -20598,13 +20598,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F292" s="5" t="str">
-        <v>38.6ms</v>
+        <v>49.0ms</v>
       </c>
       <c r="G292" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H292" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 38.6ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 49.0ms. Payload matches schema.</v>
       </c>
       <c r="I292" s="5" t="str">
         <v>PASS</v>
@@ -20630,13 +20630,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F293" s="5" t="str">
-        <v>27.1ms</v>
+        <v>52.3ms</v>
       </c>
       <c r="G293" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H293" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 27.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 52.3ms. Payload matches schema.</v>
       </c>
       <c r="I293" s="5" t="str">
         <v>PASS</v>
@@ -20662,13 +20662,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F294" s="5" t="str">
-        <v>21.8ms</v>
+        <v>58.5ms</v>
       </c>
       <c r="G294" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H294" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 21.8ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 58.5ms. Payload matches schema.</v>
       </c>
       <c r="I294" s="5" t="str">
         <v>PASS</v>
@@ -20694,13 +20694,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F295" s="5" t="str">
-        <v>31.2ms</v>
+        <v>52.8ms</v>
       </c>
       <c r="G295" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H295" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 31.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 52.8ms. Payload matches schema.</v>
       </c>
       <c r="I295" s="5" t="str">
         <v>PASS</v>
@@ -20726,13 +20726,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F296" s="5" t="str">
-        <v>51.2ms</v>
+        <v>44.8ms</v>
       </c>
       <c r="G296" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H296" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 51.2ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 44.8ms. Payload matches schema.</v>
       </c>
       <c r="I296" s="5" t="str">
         <v>PASS</v>
@@ -20758,13 +20758,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F297" s="5" t="str">
-        <v>28.0ms</v>
+        <v>21.2ms</v>
       </c>
       <c r="G297" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H297" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 28.0ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 21.2ms. Payload matches schema.</v>
       </c>
       <c r="I297" s="5" t="str">
         <v>PASS</v>
@@ -20790,13 +20790,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F298" s="5" t="str">
-        <v>51.1ms</v>
+        <v>47.6ms</v>
       </c>
       <c r="G298" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H298" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 51.1ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 47.6ms. Payload matches schema.</v>
       </c>
       <c r="I298" s="5" t="str">
         <v>PASS</v>
@@ -20822,13 +20822,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F299" s="5" t="str">
-        <v>55.4ms</v>
+        <v>53.0ms</v>
       </c>
       <c r="G299" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H299" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 55.4ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 53.0ms. Payload matches schema.</v>
       </c>
       <c r="I299" s="5" t="str">
         <v>PASS</v>
@@ -20854,13 +20854,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F300" s="5" t="str">
-        <v>50.3ms</v>
+        <v>31.1ms</v>
       </c>
       <c r="G300" s="5" t="str">
         <v>HTTP status code 200 and valid JSON payload schema returned.</v>
       </c>
       <c r="H300" s="5" t="str">
-        <v>HTTP 200 OK. Latency: 50.3ms. Payload matches schema.</v>
+        <v>HTTP 200 OK. Latency: 31.1ms. Payload matches schema.</v>
       </c>
       <c r="I300" s="5" t="str">
         <v>PASS</v>
@@ -20886,13 +20886,13 @@
         <v>N/A (Direct HTTP)</v>
       </c>
       <c r="F301" s="5" t="str">
-        <v>34.3ms</v>
+        <v>14.5ms</v>
       </c>
       <c r="G301" s="5" t="str">
         <v>HTTP status code 201 and valid JSON payload schema returned.</v>
       </c>
       <c r="H301" s="5" t="str">
-        <v>HTTP 201 OK. Latency: 34.3ms. Payload matches schema.</v>
+        <v>HTTP 201 OK. Latency: 14.5ms. Payload matches schema.</v>
       </c>
       <c r="I301" s="5" t="str">
         <v>PASS</v>
@@ -20974,7 +20974,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F2" s="5" t="str">
-        <v>30.3ms</v>
+        <v>45.2ms</v>
       </c>
       <c r="G2" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21006,7 +21006,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F3" s="5" t="str">
-        <v>23.8ms</v>
+        <v>47.5ms</v>
       </c>
       <c r="G3" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21038,7 +21038,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F4" s="5" t="str">
-        <v>20.2ms</v>
+        <v>49.2ms</v>
       </c>
       <c r="G4" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21070,7 +21070,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F5" s="5" t="str">
-        <v>34.9ms</v>
+        <v>21.2ms</v>
       </c>
       <c r="G5" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21102,7 +21102,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F6" s="5" t="str">
-        <v>55.7ms</v>
+        <v>55.5ms</v>
       </c>
       <c r="G6" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21134,7 +21134,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F7" s="5" t="str">
-        <v>36.5ms</v>
+        <v>43.2ms</v>
       </c>
       <c r="G7" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21166,7 +21166,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F8" s="5" t="str">
-        <v>38.5ms</v>
+        <v>24.2ms</v>
       </c>
       <c r="G8" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21198,7 +21198,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F9" s="5" t="str">
-        <v>23.2ms</v>
+        <v>37.1ms</v>
       </c>
       <c r="G9" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21230,7 +21230,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F10" s="5" t="str">
-        <v>47.6ms</v>
+        <v>41.6ms</v>
       </c>
       <c r="G10" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21262,7 +21262,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F11" s="5" t="str">
-        <v>48.0ms</v>
+        <v>47.9ms</v>
       </c>
       <c r="G11" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21294,7 +21294,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F12" s="5" t="str">
-        <v>32.7ms</v>
+        <v>42.4ms</v>
       </c>
       <c r="G12" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21326,7 +21326,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F13" s="5" t="str">
-        <v>27.5ms</v>
+        <v>41.7ms</v>
       </c>
       <c r="G13" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21358,7 +21358,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F14" s="5" t="str">
-        <v>42.2ms</v>
+        <v>54.1ms</v>
       </c>
       <c r="G14" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21390,7 +21390,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F15" s="5" t="str">
-        <v>36.0ms</v>
+        <v>22.4ms</v>
       </c>
       <c r="G15" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21422,7 +21422,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F16" s="5" t="str">
-        <v>54.5ms</v>
+        <v>25.0ms</v>
       </c>
       <c r="G16" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21454,7 +21454,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F17" s="5" t="str">
-        <v>35.5ms</v>
+        <v>51.3ms</v>
       </c>
       <c r="G17" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21486,7 +21486,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F18" s="5" t="str">
-        <v>47.3ms</v>
+        <v>36.0ms</v>
       </c>
       <c r="G18" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21518,7 +21518,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F19" s="5" t="str">
-        <v>56.0ms</v>
+        <v>35.2ms</v>
       </c>
       <c r="G19" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21550,7 +21550,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F20" s="5" t="str">
-        <v>27.5ms</v>
+        <v>35.4ms</v>
       </c>
       <c r="G20" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21582,7 +21582,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F21" s="5" t="str">
-        <v>48.6ms</v>
+        <v>25.2ms</v>
       </c>
       <c r="G21" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21614,7 +21614,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F22" s="5" t="str">
-        <v>20.3ms</v>
+        <v>55.0ms</v>
       </c>
       <c r="G22" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21646,7 +21646,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F23" s="5" t="str">
-        <v>23.8ms</v>
+        <v>55.6ms</v>
       </c>
       <c r="G23" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21678,7 +21678,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F24" s="5" t="str">
-        <v>38.4ms</v>
+        <v>53.8ms</v>
       </c>
       <c r="G24" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21710,7 +21710,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F25" s="5" t="str">
-        <v>34.8ms</v>
+        <v>42.1ms</v>
       </c>
       <c r="G25" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21742,7 +21742,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F26" s="5" t="str">
-        <v>31.6ms</v>
+        <v>42.5ms</v>
       </c>
       <c r="G26" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21774,7 +21774,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F27" s="5" t="str">
-        <v>33.3ms</v>
+        <v>35.1ms</v>
       </c>
       <c r="G27" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21806,7 +21806,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F28" s="5" t="str">
-        <v>55.6ms</v>
+        <v>49.6ms</v>
       </c>
       <c r="G28" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21838,7 +21838,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F29" s="5" t="str">
-        <v>50.0ms</v>
+        <v>25.4ms</v>
       </c>
       <c r="G29" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21870,7 +21870,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F30" s="5" t="str">
-        <v>58.5ms</v>
+        <v>34.9ms</v>
       </c>
       <c r="G30" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21902,7 +21902,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F31" s="5" t="str">
-        <v>52.4ms</v>
+        <v>43.3ms</v>
       </c>
       <c r="G31" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21934,7 +21934,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F32" s="5" t="str">
-        <v>32.5ms</v>
+        <v>47.4ms</v>
       </c>
       <c r="G32" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21966,7 +21966,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F33" s="5" t="str">
-        <v>40.4ms</v>
+        <v>46.3ms</v>
       </c>
       <c r="G33" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -21998,7 +21998,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F34" s="5" t="str">
-        <v>25.7ms</v>
+        <v>49.1ms</v>
       </c>
       <c r="G34" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22030,7 +22030,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F35" s="5" t="str">
-        <v>44.2ms</v>
+        <v>26.2ms</v>
       </c>
       <c r="G35" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22062,7 +22062,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F36" s="5" t="str">
-        <v>42.6ms</v>
+        <v>58.2ms</v>
       </c>
       <c r="G36" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22094,7 +22094,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F37" s="5" t="str">
-        <v>31.1ms</v>
+        <v>45.1ms</v>
       </c>
       <c r="G37" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22126,7 +22126,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F38" s="5" t="str">
-        <v>58.7ms</v>
+        <v>50.6ms</v>
       </c>
       <c r="G38" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22158,7 +22158,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F39" s="5" t="str">
-        <v>40.2ms</v>
+        <v>34.4ms</v>
       </c>
       <c r="G39" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22190,7 +22190,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F40" s="5" t="str">
-        <v>25.9ms</v>
+        <v>58.0ms</v>
       </c>
       <c r="G40" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22222,7 +22222,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F41" s="5" t="str">
-        <v>23.2ms</v>
+        <v>57.5ms</v>
       </c>
       <c r="G41" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22254,7 +22254,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F42" s="5" t="str">
-        <v>42.4ms</v>
+        <v>42.8ms</v>
       </c>
       <c r="G42" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22286,7 +22286,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F43" s="5" t="str">
-        <v>40.7ms</v>
+        <v>47.4ms</v>
       </c>
       <c r="G43" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22318,7 +22318,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F44" s="5" t="str">
-        <v>58.6ms</v>
+        <v>49.2ms</v>
       </c>
       <c r="G44" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22350,7 +22350,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F45" s="5" t="str">
-        <v>40.7ms</v>
+        <v>48.4ms</v>
       </c>
       <c r="G45" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22382,7 +22382,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F46" s="5" t="str">
-        <v>55.0ms</v>
+        <v>29.9ms</v>
       </c>
       <c r="G46" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22414,7 +22414,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F47" s="5" t="str">
-        <v>34.2ms</v>
+        <v>51.3ms</v>
       </c>
       <c r="G47" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22446,7 +22446,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F48" s="5" t="str">
-        <v>51.9ms</v>
+        <v>40.2ms</v>
       </c>
       <c r="G48" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22478,7 +22478,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F49" s="5" t="str">
-        <v>32.3ms</v>
+        <v>45.9ms</v>
       </c>
       <c r="G49" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22510,7 +22510,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F50" s="5" t="str">
-        <v>24.0ms</v>
+        <v>30.2ms</v>
       </c>
       <c r="G50" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22542,7 +22542,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F51" s="5" t="str">
-        <v>40.2ms</v>
+        <v>24.3ms</v>
       </c>
       <c r="G51" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22574,7 +22574,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F52" s="5" t="str">
-        <v>48.2ms</v>
+        <v>36.9ms</v>
       </c>
       <c r="G52" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22606,7 +22606,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F53" s="5" t="str">
-        <v>42.6ms</v>
+        <v>29.3ms</v>
       </c>
       <c r="G53" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22638,7 +22638,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F54" s="5" t="str">
-        <v>52.3ms</v>
+        <v>33.6ms</v>
       </c>
       <c r="G54" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22670,7 +22670,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F55" s="5" t="str">
-        <v>27.7ms</v>
+        <v>51.5ms</v>
       </c>
       <c r="G55" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22702,7 +22702,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F56" s="5" t="str">
-        <v>48.9ms</v>
+        <v>59.6ms</v>
       </c>
       <c r="G56" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22734,7 +22734,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F57" s="5" t="str">
-        <v>27.6ms</v>
+        <v>32.1ms</v>
       </c>
       <c r="G57" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22766,7 +22766,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F58" s="5" t="str">
-        <v>41.9ms</v>
+        <v>43.5ms</v>
       </c>
       <c r="G58" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22798,7 +22798,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F59" s="5" t="str">
-        <v>39.8ms</v>
+        <v>58.4ms</v>
       </c>
       <c r="G59" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22830,7 +22830,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F60" s="5" t="str">
-        <v>40.3ms</v>
+        <v>32.5ms</v>
       </c>
       <c r="G60" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22862,7 +22862,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F61" s="5" t="str">
-        <v>47.8ms</v>
+        <v>50.1ms</v>
       </c>
       <c r="G61" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22894,7 +22894,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F62" s="5" t="str">
-        <v>43.1ms</v>
+        <v>24.2ms</v>
       </c>
       <c r="G62" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22926,7 +22926,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F63" s="5" t="str">
-        <v>32.4ms</v>
+        <v>47.5ms</v>
       </c>
       <c r="G63" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22958,7 +22958,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F64" s="5" t="str">
-        <v>33.9ms</v>
+        <v>33.0ms</v>
       </c>
       <c r="G64" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -22990,7 +22990,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F65" s="5" t="str">
-        <v>32.9ms</v>
+        <v>32.2ms</v>
       </c>
       <c r="G65" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23022,7 +23022,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F66" s="5" t="str">
-        <v>40.8ms</v>
+        <v>54.7ms</v>
       </c>
       <c r="G66" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23054,7 +23054,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F67" s="5" t="str">
-        <v>36.8ms</v>
+        <v>25.5ms</v>
       </c>
       <c r="G67" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23086,7 +23086,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F68" s="5" t="str">
-        <v>35.9ms</v>
+        <v>20.8ms</v>
       </c>
       <c r="G68" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23118,7 +23118,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F69" s="5" t="str">
-        <v>26.2ms</v>
+        <v>20.5ms</v>
       </c>
       <c r="G69" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23150,7 +23150,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F70" s="5" t="str">
-        <v>25.5ms</v>
+        <v>39.0ms</v>
       </c>
       <c r="G70" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23182,7 +23182,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F71" s="5" t="str">
-        <v>25.1ms</v>
+        <v>31.1ms</v>
       </c>
       <c r="G71" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23214,7 +23214,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F72" s="5" t="str">
-        <v>30.6ms</v>
+        <v>51.8ms</v>
       </c>
       <c r="G72" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23246,7 +23246,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F73" s="5" t="str">
-        <v>27.3ms</v>
+        <v>34.7ms</v>
       </c>
       <c r="G73" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23278,7 +23278,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F74" s="5" t="str">
-        <v>22.1ms</v>
+        <v>44.3ms</v>
       </c>
       <c r="G74" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23310,7 +23310,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F75" s="5" t="str">
-        <v>24.4ms</v>
+        <v>30.8ms</v>
       </c>
       <c r="G75" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23342,7 +23342,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F76" s="5" t="str">
-        <v>28.7ms</v>
+        <v>31.9ms</v>
       </c>
       <c r="G76" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23374,7 +23374,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F77" s="5" t="str">
-        <v>53.1ms</v>
+        <v>26.6ms</v>
       </c>
       <c r="G77" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23406,7 +23406,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F78" s="5" t="str">
-        <v>29.0ms</v>
+        <v>34.4ms</v>
       </c>
       <c r="G78" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23438,7 +23438,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F79" s="5" t="str">
-        <v>42.5ms</v>
+        <v>32.9ms</v>
       </c>
       <c r="G79" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23470,7 +23470,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F80" s="5" t="str">
-        <v>22.4ms</v>
+        <v>40.1ms</v>
       </c>
       <c r="G80" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23502,7 +23502,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F81" s="5" t="str">
-        <v>35.1ms</v>
+        <v>54.2ms</v>
       </c>
       <c r="G81" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23534,7 +23534,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F82" s="5" t="str">
-        <v>24.7ms</v>
+        <v>35.3ms</v>
       </c>
       <c r="G82" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23566,7 +23566,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F83" s="5" t="str">
-        <v>57.8ms</v>
+        <v>49.7ms</v>
       </c>
       <c r="G83" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23598,7 +23598,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F84" s="5" t="str">
-        <v>47.6ms</v>
+        <v>43.9ms</v>
       </c>
       <c r="G84" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23630,7 +23630,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F85" s="5" t="str">
-        <v>34.2ms</v>
+        <v>47.9ms</v>
       </c>
       <c r="G85" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23662,7 +23662,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F86" s="5" t="str">
-        <v>47.8ms</v>
+        <v>40.6ms</v>
       </c>
       <c r="G86" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23694,7 +23694,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F87" s="5" t="str">
-        <v>22.1ms</v>
+        <v>26.5ms</v>
       </c>
       <c r="G87" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23726,7 +23726,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F88" s="5" t="str">
-        <v>40.0ms</v>
+        <v>47.9ms</v>
       </c>
       <c r="G88" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23758,7 +23758,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F89" s="5" t="str">
-        <v>45.8ms</v>
+        <v>37.4ms</v>
       </c>
       <c r="G89" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23790,7 +23790,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F90" s="5" t="str">
-        <v>55.7ms</v>
+        <v>49.5ms</v>
       </c>
       <c r="G90" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23822,7 +23822,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F91" s="5" t="str">
-        <v>40.8ms</v>
+        <v>45.7ms</v>
       </c>
       <c r="G91" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23854,7 +23854,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F92" s="5" t="str">
-        <v>31.7ms</v>
+        <v>52.4ms</v>
       </c>
       <c r="G92" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23886,7 +23886,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F93" s="5" t="str">
-        <v>56.5ms</v>
+        <v>33.9ms</v>
       </c>
       <c r="G93" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23918,7 +23918,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F94" s="5" t="str">
-        <v>38.2ms</v>
+        <v>30.1ms</v>
       </c>
       <c r="G94" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23950,7 +23950,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F95" s="5" t="str">
-        <v>30.1ms</v>
+        <v>56.7ms</v>
       </c>
       <c r="G95" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -23982,7 +23982,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F96" s="5" t="str">
-        <v>34.8ms</v>
+        <v>27.3ms</v>
       </c>
       <c r="G96" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24014,7 +24014,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F97" s="5" t="str">
-        <v>54.9ms</v>
+        <v>59.6ms</v>
       </c>
       <c r="G97" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24046,7 +24046,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F98" s="5" t="str">
-        <v>23.7ms</v>
+        <v>57.6ms</v>
       </c>
       <c r="G98" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24078,7 +24078,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F99" s="5" t="str">
-        <v>42.9ms</v>
+        <v>37.9ms</v>
       </c>
       <c r="G99" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24110,7 +24110,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F100" s="5" t="str">
-        <v>39.6ms</v>
+        <v>20.3ms</v>
       </c>
       <c r="G100" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24142,7 +24142,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F101" s="5" t="str">
-        <v>38.6ms</v>
+        <v>48.9ms</v>
       </c>
       <c r="G101" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24174,7 +24174,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F102" s="5" t="str">
-        <v>27.4ms</v>
+        <v>43.6ms</v>
       </c>
       <c r="G102" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24206,7 +24206,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F103" s="5" t="str">
-        <v>26.2ms</v>
+        <v>31.3ms</v>
       </c>
       <c r="G103" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24238,7 +24238,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F104" s="5" t="str">
-        <v>35.7ms</v>
+        <v>22.8ms</v>
       </c>
       <c r="G104" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24270,7 +24270,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F105" s="5" t="str">
-        <v>39.2ms</v>
+        <v>21.8ms</v>
       </c>
       <c r="G105" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24302,7 +24302,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F106" s="5" t="str">
-        <v>49.5ms</v>
+        <v>43.2ms</v>
       </c>
       <c r="G106" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24334,7 +24334,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F107" s="5" t="str">
-        <v>49.6ms</v>
+        <v>57.8ms</v>
       </c>
       <c r="G107" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24366,7 +24366,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F108" s="5" t="str">
-        <v>28.0ms</v>
+        <v>29.3ms</v>
       </c>
       <c r="G108" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24398,7 +24398,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F109" s="5" t="str">
-        <v>33.4ms</v>
+        <v>22.0ms</v>
       </c>
       <c r="G109" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24430,7 +24430,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F110" s="5" t="str">
-        <v>25.0ms</v>
+        <v>28.4ms</v>
       </c>
       <c r="G110" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24462,7 +24462,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F111" s="5" t="str">
-        <v>24.6ms</v>
+        <v>29.2ms</v>
       </c>
       <c r="G111" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24494,7 +24494,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F112" s="5" t="str">
-        <v>31.9ms</v>
+        <v>59.9ms</v>
       </c>
       <c r="G112" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24526,7 +24526,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F113" s="5" t="str">
-        <v>37.3ms</v>
+        <v>48.1ms</v>
       </c>
       <c r="G113" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24558,7 +24558,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F114" s="5" t="str">
-        <v>42.4ms</v>
+        <v>33.6ms</v>
       </c>
       <c r="G114" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24590,7 +24590,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F115" s="5" t="str">
-        <v>20.8ms</v>
+        <v>32.2ms</v>
       </c>
       <c r="G115" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24622,7 +24622,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F116" s="5" t="str">
-        <v>59.7ms</v>
+        <v>39.6ms</v>
       </c>
       <c r="G116" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24654,7 +24654,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F117" s="5" t="str">
-        <v>34.8ms</v>
+        <v>46.0ms</v>
       </c>
       <c r="G117" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24686,7 +24686,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F118" s="5" t="str">
-        <v>36.2ms</v>
+        <v>53.8ms</v>
       </c>
       <c r="G118" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24718,7 +24718,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F119" s="5" t="str">
-        <v>57.5ms</v>
+        <v>43.8ms</v>
       </c>
       <c r="G119" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24750,7 +24750,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F120" s="5" t="str">
-        <v>59.0ms</v>
+        <v>47.0ms</v>
       </c>
       <c r="G120" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24782,7 +24782,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F121" s="5" t="str">
-        <v>48.8ms</v>
+        <v>35.6ms</v>
       </c>
       <c r="G121" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24814,7 +24814,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F122" s="5" t="str">
-        <v>22.4ms</v>
+        <v>32.2ms</v>
       </c>
       <c r="G122" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24846,7 +24846,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F123" s="5" t="str">
-        <v>52.2ms</v>
+        <v>38.5ms</v>
       </c>
       <c r="G123" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24878,7 +24878,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F124" s="5" t="str">
-        <v>54.0ms</v>
+        <v>47.7ms</v>
       </c>
       <c r="G124" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24910,7 +24910,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F125" s="5" t="str">
-        <v>28.9ms</v>
+        <v>41.2ms</v>
       </c>
       <c r="G125" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24942,7 +24942,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F126" s="5" t="str">
-        <v>27.6ms</v>
+        <v>45.0ms</v>
       </c>
       <c r="G126" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -24974,7 +24974,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F127" s="5" t="str">
-        <v>29.9ms</v>
+        <v>54.2ms</v>
       </c>
       <c r="G127" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25006,7 +25006,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F128" s="5" t="str">
-        <v>58.7ms</v>
+        <v>55.7ms</v>
       </c>
       <c r="G128" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25038,7 +25038,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F129" s="5" t="str">
-        <v>48.3ms</v>
+        <v>31.5ms</v>
       </c>
       <c r="G129" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25070,7 +25070,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F130" s="5" t="str">
-        <v>54.4ms</v>
+        <v>35.7ms</v>
       </c>
       <c r="G130" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25102,7 +25102,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F131" s="5" t="str">
-        <v>51.8ms</v>
+        <v>58.7ms</v>
       </c>
       <c r="G131" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25134,7 +25134,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F132" s="5" t="str">
-        <v>50.3ms</v>
+        <v>41.5ms</v>
       </c>
       <c r="G132" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25166,7 +25166,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F133" s="5" t="str">
-        <v>29.8ms</v>
+        <v>48.7ms</v>
       </c>
       <c r="G133" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25198,7 +25198,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F134" s="5" t="str">
-        <v>24.7ms</v>
+        <v>43.4ms</v>
       </c>
       <c r="G134" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25230,7 +25230,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F135" s="5" t="str">
-        <v>51.1ms</v>
+        <v>38.2ms</v>
       </c>
       <c r="G135" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25262,7 +25262,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F136" s="5" t="str">
-        <v>51.0ms</v>
+        <v>42.6ms</v>
       </c>
       <c r="G136" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25294,7 +25294,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F137" s="5" t="str">
-        <v>53.8ms</v>
+        <v>46.7ms</v>
       </c>
       <c r="G137" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25326,7 +25326,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F138" s="5" t="str">
-        <v>26.6ms</v>
+        <v>51.7ms</v>
       </c>
       <c r="G138" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25358,7 +25358,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F139" s="5" t="str">
-        <v>34.1ms</v>
+        <v>59.9ms</v>
       </c>
       <c r="G139" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25390,7 +25390,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F140" s="5" t="str">
-        <v>43.2ms</v>
+        <v>32.8ms</v>
       </c>
       <c r="G140" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25422,7 +25422,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F141" s="5" t="str">
-        <v>45.1ms</v>
+        <v>37.4ms</v>
       </c>
       <c r="G141" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25454,7 +25454,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F142" s="5" t="str">
-        <v>51.8ms</v>
+        <v>33.0ms</v>
       </c>
       <c r="G142" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25486,7 +25486,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F143" s="5" t="str">
-        <v>58.3ms</v>
+        <v>31.5ms</v>
       </c>
       <c r="G143" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25518,7 +25518,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F144" s="5" t="str">
-        <v>59.7ms</v>
+        <v>59.4ms</v>
       </c>
       <c r="G144" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25550,7 +25550,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F145" s="5" t="str">
-        <v>20.1ms</v>
+        <v>58.4ms</v>
       </c>
       <c r="G145" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25582,7 +25582,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F146" s="5" t="str">
-        <v>42.3ms</v>
+        <v>53.3ms</v>
       </c>
       <c r="G146" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25614,7 +25614,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F147" s="5" t="str">
-        <v>40.7ms</v>
+        <v>32.3ms</v>
       </c>
       <c r="G147" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25646,7 +25646,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F148" s="5" t="str">
-        <v>48.7ms</v>
+        <v>38.7ms</v>
       </c>
       <c r="G148" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25678,7 +25678,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F149" s="5" t="str">
-        <v>23.2ms</v>
+        <v>38.6ms</v>
       </c>
       <c r="G149" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25710,7 +25710,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F150" s="5" t="str">
-        <v>26.4ms</v>
+        <v>51.9ms</v>
       </c>
       <c r="G150" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25742,7 +25742,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F151" s="5" t="str">
-        <v>22.3ms</v>
+        <v>42.7ms</v>
       </c>
       <c r="G151" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25774,7 +25774,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F152" s="5" t="str">
-        <v>39.4ms</v>
+        <v>39.7ms</v>
       </c>
       <c r="G152" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25806,7 +25806,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F153" s="5" t="str">
-        <v>55.6ms</v>
+        <v>28.9ms</v>
       </c>
       <c r="G153" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25838,7 +25838,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F154" s="5" t="str">
-        <v>57.9ms</v>
+        <v>55.2ms</v>
       </c>
       <c r="G154" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25870,7 +25870,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F155" s="5" t="str">
-        <v>27.6ms</v>
+        <v>43.8ms</v>
       </c>
       <c r="G155" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25902,7 +25902,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F156" s="5" t="str">
-        <v>55.7ms</v>
+        <v>43.8ms</v>
       </c>
       <c r="G156" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25934,7 +25934,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F157" s="5" t="str">
-        <v>52.7ms</v>
+        <v>39.3ms</v>
       </c>
       <c r="G157" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25966,7 +25966,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F158" s="5" t="str">
-        <v>28.0ms</v>
+        <v>40.9ms</v>
       </c>
       <c r="G158" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -25998,7 +25998,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F159" s="5" t="str">
-        <v>24.3ms</v>
+        <v>57.2ms</v>
       </c>
       <c r="G159" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26030,7 +26030,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F160" s="5" t="str">
-        <v>51.2ms</v>
+        <v>30.7ms</v>
       </c>
       <c r="G160" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26062,7 +26062,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F161" s="5" t="str">
-        <v>25.5ms</v>
+        <v>47.0ms</v>
       </c>
       <c r="G161" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26094,7 +26094,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F162" s="5" t="str">
-        <v>22.2ms</v>
+        <v>26.9ms</v>
       </c>
       <c r="G162" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26126,7 +26126,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F163" s="5" t="str">
-        <v>25.9ms</v>
+        <v>48.3ms</v>
       </c>
       <c r="G163" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26158,7 +26158,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F164" s="5" t="str">
-        <v>22.4ms</v>
+        <v>43.2ms</v>
       </c>
       <c r="G164" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26190,7 +26190,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F165" s="5" t="str">
-        <v>50.8ms</v>
+        <v>53.8ms</v>
       </c>
       <c r="G165" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26222,7 +26222,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F166" s="5" t="str">
-        <v>38.5ms</v>
+        <v>50.9ms</v>
       </c>
       <c r="G166" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26254,7 +26254,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F167" s="5" t="str">
-        <v>44.9ms</v>
+        <v>26.3ms</v>
       </c>
       <c r="G167" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26286,7 +26286,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F168" s="5" t="str">
-        <v>36.3ms</v>
+        <v>54.5ms</v>
       </c>
       <c r="G168" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26318,7 +26318,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F169" s="5" t="str">
-        <v>24.2ms</v>
+        <v>48.2ms</v>
       </c>
       <c r="G169" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26350,7 +26350,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F170" s="5" t="str">
-        <v>44.1ms</v>
+        <v>47.7ms</v>
       </c>
       <c r="G170" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26382,7 +26382,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F171" s="5" t="str">
-        <v>50.9ms</v>
+        <v>34.8ms</v>
       </c>
       <c r="G171" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26414,7 +26414,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F172" s="5" t="str">
-        <v>35.0ms</v>
+        <v>23.6ms</v>
       </c>
       <c r="G172" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26446,7 +26446,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F173" s="5" t="str">
-        <v>54.6ms</v>
+        <v>40.9ms</v>
       </c>
       <c r="G173" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26478,7 +26478,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F174" s="5" t="str">
-        <v>24.3ms</v>
+        <v>20.2ms</v>
       </c>
       <c r="G174" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26510,7 +26510,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F175" s="5" t="str">
-        <v>49.3ms</v>
+        <v>22.3ms</v>
       </c>
       <c r="G175" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26542,7 +26542,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F176" s="5" t="str">
-        <v>33.7ms</v>
+        <v>39.5ms</v>
       </c>
       <c r="G176" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26574,7 +26574,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F177" s="5" t="str">
-        <v>34.5ms</v>
+        <v>47.3ms</v>
       </c>
       <c r="G177" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26606,7 +26606,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F178" s="5" t="str">
-        <v>42.2ms</v>
+        <v>27.6ms</v>
       </c>
       <c r="G178" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26638,7 +26638,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F179" s="5" t="str">
-        <v>21.5ms</v>
+        <v>33.8ms</v>
       </c>
       <c r="G179" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26670,7 +26670,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F180" s="5" t="str">
-        <v>38.2ms</v>
+        <v>35.6ms</v>
       </c>
       <c r="G180" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26702,7 +26702,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F181" s="5" t="str">
-        <v>34.6ms</v>
+        <v>42.4ms</v>
       </c>
       <c r="G181" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26734,7 +26734,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F182" s="5" t="str">
-        <v>56.0ms</v>
+        <v>30.2ms</v>
       </c>
       <c r="G182" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26766,7 +26766,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F183" s="5" t="str">
-        <v>57.2ms</v>
+        <v>26.7ms</v>
       </c>
       <c r="G183" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26798,7 +26798,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F184" s="5" t="str">
-        <v>54.4ms</v>
+        <v>22.1ms</v>
       </c>
       <c r="G184" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26830,7 +26830,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F185" s="5" t="str">
-        <v>39.2ms</v>
+        <v>26.5ms</v>
       </c>
       <c r="G185" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26862,7 +26862,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F186" s="5" t="str">
-        <v>43.1ms</v>
+        <v>55.5ms</v>
       </c>
       <c r="G186" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26894,7 +26894,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F187" s="5" t="str">
-        <v>28.4ms</v>
+        <v>58.1ms</v>
       </c>
       <c r="G187" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26926,7 +26926,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F188" s="5" t="str">
-        <v>38.0ms</v>
+        <v>22.3ms</v>
       </c>
       <c r="G188" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26958,7 +26958,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F189" s="5" t="str">
-        <v>34.9ms</v>
+        <v>55.9ms</v>
       </c>
       <c r="G189" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -26990,7 +26990,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F190" s="5" t="str">
-        <v>57.2ms</v>
+        <v>54.8ms</v>
       </c>
       <c r="G190" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27022,7 +27022,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F191" s="5" t="str">
-        <v>33.5ms</v>
+        <v>39.1ms</v>
       </c>
       <c r="G191" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27054,7 +27054,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F192" s="5" t="str">
-        <v>28.1ms</v>
+        <v>37.0ms</v>
       </c>
       <c r="G192" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27086,7 +27086,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F193" s="5" t="str">
-        <v>38.3ms</v>
+        <v>52.8ms</v>
       </c>
       <c r="G193" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27118,7 +27118,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F194" s="5" t="str">
-        <v>42.9ms</v>
+        <v>39.5ms</v>
       </c>
       <c r="G194" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27150,7 +27150,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F195" s="5" t="str">
-        <v>22.8ms</v>
+        <v>41.9ms</v>
       </c>
       <c r="G195" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27182,7 +27182,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F196" s="5" t="str">
-        <v>50.9ms</v>
+        <v>27.3ms</v>
       </c>
       <c r="G196" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27214,7 +27214,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F197" s="5" t="str">
-        <v>46.7ms</v>
+        <v>49.7ms</v>
       </c>
       <c r="G197" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27246,7 +27246,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F198" s="5" t="str">
-        <v>53.7ms</v>
+        <v>26.1ms</v>
       </c>
       <c r="G198" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27278,7 +27278,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F199" s="5" t="str">
-        <v>48.4ms</v>
+        <v>30.4ms</v>
       </c>
       <c r="G199" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27310,7 +27310,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F200" s="5" t="str">
-        <v>53.7ms</v>
+        <v>57.7ms</v>
       </c>
       <c r="G200" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27342,7 +27342,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F201" s="5" t="str">
-        <v>39.2ms</v>
+        <v>33.0ms</v>
       </c>
       <c r="G201" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27374,7 +27374,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F202" s="5" t="str">
-        <v>52.4ms</v>
+        <v>35.2ms</v>
       </c>
       <c r="G202" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27406,7 +27406,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F203" s="5" t="str">
-        <v>47.1ms</v>
+        <v>37.3ms</v>
       </c>
       <c r="G203" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27438,7 +27438,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F204" s="5" t="str">
-        <v>20.7ms</v>
+        <v>22.5ms</v>
       </c>
       <c r="G204" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27470,7 +27470,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F205" s="5" t="str">
-        <v>43.6ms</v>
+        <v>25.8ms</v>
       </c>
       <c r="G205" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27502,7 +27502,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F206" s="5" t="str">
-        <v>25.4ms</v>
+        <v>29.5ms</v>
       </c>
       <c r="G206" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27534,7 +27534,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F207" s="5" t="str">
-        <v>52.1ms</v>
+        <v>31.3ms</v>
       </c>
       <c r="G207" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27566,7 +27566,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F208" s="5" t="str">
-        <v>26.8ms</v>
+        <v>33.0ms</v>
       </c>
       <c r="G208" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27598,7 +27598,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F209" s="5" t="str">
-        <v>59.8ms</v>
+        <v>56.2ms</v>
       </c>
       <c r="G209" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27630,7 +27630,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F210" s="5" t="str">
-        <v>45.9ms</v>
+        <v>58.2ms</v>
       </c>
       <c r="G210" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27662,7 +27662,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F211" s="5" t="str">
-        <v>54.8ms</v>
+        <v>50.9ms</v>
       </c>
       <c r="G211" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27694,7 +27694,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F212" s="5" t="str">
-        <v>30.3ms</v>
+        <v>42.3ms</v>
       </c>
       <c r="G212" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27726,7 +27726,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F213" s="5" t="str">
-        <v>41.9ms</v>
+        <v>52.4ms</v>
       </c>
       <c r="G213" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27758,7 +27758,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F214" s="5" t="str">
-        <v>52.1ms</v>
+        <v>20.1ms</v>
       </c>
       <c r="G214" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27790,7 +27790,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F215" s="5" t="str">
-        <v>42.1ms</v>
+        <v>22.5ms</v>
       </c>
       <c r="G215" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27822,7 +27822,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F216" s="5" t="str">
-        <v>40.4ms</v>
+        <v>36.3ms</v>
       </c>
       <c r="G216" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27854,7 +27854,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F217" s="5" t="str">
-        <v>58.3ms</v>
+        <v>48.3ms</v>
       </c>
       <c r="G217" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27886,7 +27886,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F218" s="5" t="str">
-        <v>36.2ms</v>
+        <v>33.2ms</v>
       </c>
       <c r="G218" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27918,7 +27918,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F219" s="5" t="str">
-        <v>48.8ms</v>
+        <v>38.7ms</v>
       </c>
       <c r="G219" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27950,7 +27950,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F220" s="5" t="str">
-        <v>52.4ms</v>
+        <v>35.8ms</v>
       </c>
       <c r="G220" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -27982,7 +27982,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F221" s="5" t="str">
-        <v>57.8ms</v>
+        <v>46.0ms</v>
       </c>
       <c r="G221" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28014,7 +28014,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F222" s="5" t="str">
-        <v>53.0ms</v>
+        <v>47.4ms</v>
       </c>
       <c r="G222" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28046,7 +28046,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F223" s="5" t="str">
-        <v>36.6ms</v>
+        <v>43.8ms</v>
       </c>
       <c r="G223" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28078,7 +28078,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F224" s="5" t="str">
-        <v>36.4ms</v>
+        <v>56.2ms</v>
       </c>
       <c r="G224" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28110,7 +28110,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F225" s="5" t="str">
-        <v>46.0ms</v>
+        <v>24.3ms</v>
       </c>
       <c r="G225" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28142,7 +28142,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F226" s="5" t="str">
-        <v>23.4ms</v>
+        <v>45.5ms</v>
       </c>
       <c r="G226" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28174,7 +28174,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F227" s="5" t="str">
-        <v>33.3ms</v>
+        <v>56.0ms</v>
       </c>
       <c r="G227" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28206,7 +28206,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F228" s="5" t="str">
-        <v>34.4ms</v>
+        <v>29.5ms</v>
       </c>
       <c r="G228" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28238,7 +28238,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F229" s="5" t="str">
-        <v>24.9ms</v>
+        <v>23.0ms</v>
       </c>
       <c r="G229" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28270,7 +28270,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F230" s="5" t="str">
-        <v>24.9ms</v>
+        <v>31.5ms</v>
       </c>
       <c r="G230" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28302,7 +28302,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F231" s="5" t="str">
-        <v>54.0ms</v>
+        <v>23.9ms</v>
       </c>
       <c r="G231" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28334,7 +28334,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F232" s="5" t="str">
-        <v>41.2ms</v>
+        <v>54.5ms</v>
       </c>
       <c r="G232" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28366,7 +28366,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F233" s="5" t="str">
-        <v>58.2ms</v>
+        <v>29.7ms</v>
       </c>
       <c r="G233" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28398,7 +28398,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F234" s="5" t="str">
-        <v>34.0ms</v>
+        <v>20.7ms</v>
       </c>
       <c r="G234" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28430,7 +28430,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F235" s="5" t="str">
-        <v>46.7ms</v>
+        <v>53.3ms</v>
       </c>
       <c r="G235" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28462,7 +28462,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F236" s="5" t="str">
-        <v>40.4ms</v>
+        <v>25.7ms</v>
       </c>
       <c r="G236" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28494,7 +28494,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F237" s="5" t="str">
-        <v>29.0ms</v>
+        <v>23.8ms</v>
       </c>
       <c r="G237" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28526,7 +28526,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F238" s="5" t="str">
-        <v>58.0ms</v>
+        <v>59.5ms</v>
       </c>
       <c r="G238" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28558,7 +28558,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F239" s="5" t="str">
-        <v>55.8ms</v>
+        <v>31.7ms</v>
       </c>
       <c r="G239" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28590,7 +28590,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F240" s="5" t="str">
-        <v>47.1ms</v>
+        <v>34.1ms</v>
       </c>
       <c r="G240" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28622,7 +28622,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F241" s="5" t="str">
-        <v>47.0ms</v>
+        <v>50.1ms</v>
       </c>
       <c r="G241" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28654,7 +28654,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F242" s="5" t="str">
-        <v>52.4ms</v>
+        <v>49.1ms</v>
       </c>
       <c r="G242" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28686,7 +28686,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F243" s="5" t="str">
-        <v>31.8ms</v>
+        <v>55.6ms</v>
       </c>
       <c r="G243" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28718,7 +28718,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F244" s="5" t="str">
-        <v>46.6ms</v>
+        <v>44.2ms</v>
       </c>
       <c r="G244" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28750,7 +28750,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F245" s="5" t="str">
-        <v>57.3ms</v>
+        <v>50.9ms</v>
       </c>
       <c r="G245" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28782,7 +28782,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F246" s="5" t="str">
-        <v>22.0ms</v>
+        <v>32.9ms</v>
       </c>
       <c r="G246" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28814,7 +28814,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F247" s="5" t="str">
-        <v>47.3ms</v>
+        <v>42.8ms</v>
       </c>
       <c r="G247" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28846,7 +28846,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F248" s="5" t="str">
-        <v>52.2ms</v>
+        <v>49.8ms</v>
       </c>
       <c r="G248" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28878,7 +28878,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F249" s="5" t="str">
-        <v>58.8ms</v>
+        <v>36.8ms</v>
       </c>
       <c r="G249" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28910,7 +28910,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F250" s="5" t="str">
-        <v>47.3ms</v>
+        <v>30.4ms</v>
       </c>
       <c r="G250" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28942,7 +28942,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F251" s="5" t="str">
-        <v>56.1ms</v>
+        <v>57.7ms</v>
       </c>
       <c r="G251" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -28974,7 +28974,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F252" s="5" t="str">
-        <v>38.1ms</v>
+        <v>43.0ms</v>
       </c>
       <c r="G252" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29006,7 +29006,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F253" s="5" t="str">
-        <v>24.3ms</v>
+        <v>32.1ms</v>
       </c>
       <c r="G253" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29038,7 +29038,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F254" s="5" t="str">
-        <v>39.2ms</v>
+        <v>40.5ms</v>
       </c>
       <c r="G254" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29070,7 +29070,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F255" s="5" t="str">
-        <v>58.7ms</v>
+        <v>23.1ms</v>
       </c>
       <c r="G255" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29102,7 +29102,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F256" s="5" t="str">
-        <v>40.6ms</v>
+        <v>29.4ms</v>
       </c>
       <c r="G256" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29134,7 +29134,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F257" s="5" t="str">
-        <v>29.5ms</v>
+        <v>23.7ms</v>
       </c>
       <c r="G257" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29166,7 +29166,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F258" s="5" t="str">
-        <v>57.9ms</v>
+        <v>31.0ms</v>
       </c>
       <c r="G258" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29198,7 +29198,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F259" s="5" t="str">
-        <v>54.7ms</v>
+        <v>38.8ms</v>
       </c>
       <c r="G259" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29230,7 +29230,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F260" s="5" t="str">
-        <v>55.9ms</v>
+        <v>29.7ms</v>
       </c>
       <c r="G260" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29262,7 +29262,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F261" s="5" t="str">
-        <v>43.2ms</v>
+        <v>33.6ms</v>
       </c>
       <c r="G261" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29294,7 +29294,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F262" s="5" t="str">
-        <v>25.5ms</v>
+        <v>38.9ms</v>
       </c>
       <c r="G262" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29326,7 +29326,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F263" s="5" t="str">
-        <v>42.1ms</v>
+        <v>53.4ms</v>
       </c>
       <c r="G263" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29358,7 +29358,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F264" s="5" t="str">
-        <v>58.7ms</v>
+        <v>40.9ms</v>
       </c>
       <c r="G264" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29390,7 +29390,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F265" s="5" t="str">
-        <v>42.0ms</v>
+        <v>23.2ms</v>
       </c>
       <c r="G265" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29422,7 +29422,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F266" s="5" t="str">
-        <v>57.7ms</v>
+        <v>35.8ms</v>
       </c>
       <c r="G266" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29454,7 +29454,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F267" s="5" t="str">
-        <v>48.5ms</v>
+        <v>46.3ms</v>
       </c>
       <c r="G267" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29486,7 +29486,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F268" s="5" t="str">
-        <v>57.5ms</v>
+        <v>50.8ms</v>
       </c>
       <c r="G268" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29518,7 +29518,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F269" s="5" t="str">
-        <v>53.6ms</v>
+        <v>25.9ms</v>
       </c>
       <c r="G269" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29550,7 +29550,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F270" s="5" t="str">
-        <v>53.8ms</v>
+        <v>37.5ms</v>
       </c>
       <c r="G270" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29582,7 +29582,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F271" s="5" t="str">
-        <v>50.9ms</v>
+        <v>44.3ms</v>
       </c>
       <c r="G271" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29614,7 +29614,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F272" s="5" t="str">
-        <v>52.9ms</v>
+        <v>39.8ms</v>
       </c>
       <c r="G272" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29646,7 +29646,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F273" s="5" t="str">
-        <v>33.6ms</v>
+        <v>42.5ms</v>
       </c>
       <c r="G273" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29678,7 +29678,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F274" s="5" t="str">
-        <v>23.1ms</v>
+        <v>28.5ms</v>
       </c>
       <c r="G274" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29710,7 +29710,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F275" s="5" t="str">
-        <v>20.9ms</v>
+        <v>43.3ms</v>
       </c>
       <c r="G275" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29742,7 +29742,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F276" s="5" t="str">
-        <v>33.8ms</v>
+        <v>43.3ms</v>
       </c>
       <c r="G276" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29774,7 +29774,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F277" s="5" t="str">
-        <v>50.5ms</v>
+        <v>21.0ms</v>
       </c>
       <c r="G277" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29806,7 +29806,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F278" s="5" t="str">
-        <v>50.3ms</v>
+        <v>38.6ms</v>
       </c>
       <c r="G278" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29838,7 +29838,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F279" s="5" t="str">
-        <v>25.7ms</v>
+        <v>36.0ms</v>
       </c>
       <c r="G279" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29870,7 +29870,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F280" s="5" t="str">
-        <v>39.3ms</v>
+        <v>30.6ms</v>
       </c>
       <c r="G280" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29902,7 +29902,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F281" s="5" t="str">
-        <v>53.7ms</v>
+        <v>33.6ms</v>
       </c>
       <c r="G281" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29934,7 +29934,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F282" s="5" t="str">
-        <v>51.4ms</v>
+        <v>50.3ms</v>
       </c>
       <c r="G282" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29966,7 +29966,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F283" s="5" t="str">
-        <v>37.6ms</v>
+        <v>25.3ms</v>
       </c>
       <c r="G283" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -29998,7 +29998,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F284" s="5" t="str">
-        <v>50.1ms</v>
+        <v>54.4ms</v>
       </c>
       <c r="G284" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30030,7 +30030,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F285" s="5" t="str">
-        <v>30.9ms</v>
+        <v>54.0ms</v>
       </c>
       <c r="G285" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30062,7 +30062,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F286" s="5" t="str">
-        <v>27.8ms</v>
+        <v>40.4ms</v>
       </c>
       <c r="G286" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30094,7 +30094,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F287" s="5" t="str">
-        <v>27.8ms</v>
+        <v>40.9ms</v>
       </c>
       <c r="G287" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30126,7 +30126,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F288" s="5" t="str">
-        <v>26.1ms</v>
+        <v>49.9ms</v>
       </c>
       <c r="G288" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30158,7 +30158,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F289" s="5" t="str">
-        <v>36.4ms</v>
+        <v>20.8ms</v>
       </c>
       <c r="G289" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30190,7 +30190,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F290" s="5" t="str">
-        <v>46.6ms</v>
+        <v>40.9ms</v>
       </c>
       <c r="G290" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30222,7 +30222,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F291" s="5" t="str">
-        <v>31.5ms</v>
+        <v>39.4ms</v>
       </c>
       <c r="G291" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30254,7 +30254,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F292" s="5" t="str">
-        <v>27.9ms</v>
+        <v>30.2ms</v>
       </c>
       <c r="G292" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30286,7 +30286,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F293" s="5" t="str">
-        <v>27.4ms</v>
+        <v>30.8ms</v>
       </c>
       <c r="G293" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30318,7 +30318,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F294" s="5" t="str">
-        <v>57.0ms</v>
+        <v>29.1ms</v>
       </c>
       <c r="G294" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30350,7 +30350,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F295" s="5" t="str">
-        <v>43.4ms</v>
+        <v>45.6ms</v>
       </c>
       <c r="G295" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30382,7 +30382,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F296" s="5" t="str">
-        <v>28.8ms</v>
+        <v>47.6ms</v>
       </c>
       <c r="G296" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30414,7 +30414,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F297" s="5" t="str">
-        <v>43.5ms</v>
+        <v>51.3ms</v>
       </c>
       <c r="G297" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30446,7 +30446,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F298" s="5" t="str">
-        <v>50.5ms</v>
+        <v>55.5ms</v>
       </c>
       <c r="G298" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30478,7 +30478,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F299" s="5" t="str">
-        <v>23.7ms</v>
+        <v>29.0ms</v>
       </c>
       <c r="G299" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30510,7 +30510,7 @@
         <v>Android (UiAutomator2)</v>
       </c>
       <c r="F300" s="5" t="str">
-        <v>55.9ms</v>
+        <v>33.6ms</v>
       </c>
       <c r="G300" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30542,7 +30542,7 @@
         <v>iOS (XCUITest)</v>
       </c>
       <c r="F301" s="5" t="str">
-        <v>23.0ms</v>
+        <v>40.8ms</v>
       </c>
       <c r="G301" s="5" t="str">
         <v>Element located and mobile action completed successfully.</v>
@@ -30610,7 +30610,7 @@
         <v>Throughput (Req/Sec)</v>
       </c>
       <c r="B5" s="5" t="str">
-        <v>15.29 req/s</v>
+        <v>11.81 req/s</v>
       </c>
     </row>
     <row r="6">
@@ -30618,7 +30618,7 @@
         <v>Average Latency</v>
       </c>
       <c r="B6" s="5" t="str">
-        <v>65.42 ms</v>
+        <v>84.62 ms</v>
       </c>
     </row>
     <row r="7">
@@ -30626,7 +30626,7 @@
         <v>Min / Max Latency</v>
       </c>
       <c r="B7" s="5" t="str">
-        <v>43 ms / 260 ms</v>
+        <v>45 ms / 577 ms</v>
       </c>
     </row>
     <row r="8">
@@ -30634,7 +30634,7 @@
         <v>P50 / P90 / P99 Latency</v>
       </c>
       <c r="B8" s="5" t="str">
-        <v>59 ms / 87 ms / 260 ms</v>
+        <v>68 ms / 106 ms / 577 ms</v>
       </c>
     </row>
     <row r="9">
